--- a/assets/contabilizacion.xlsx
+++ b/assets/contabilizacion.xlsx
@@ -989,8 +989,16 @@
       <c r="B2" s="36" t="n">
         <v>45236</v>
       </c>
-      <c r="C2" s="37" t="n"/>
-      <c r="D2" s="37" t="n"/>
+      <c r="C2" s="37" t="inlineStr">
+        <is>
+          <t>nnnn</t>
+        </is>
+      </c>
+      <c r="D2" s="37" t="inlineStr">
+        <is>
+          <t>21244</t>
+        </is>
+      </c>
       <c r="E2" s="28" t="inlineStr">
         <is>
           <t>adelanto jose</t>
@@ -1028,8 +1036,16 @@
       <c r="B3" s="36" t="n">
         <v>45236</v>
       </c>
-      <c r="C3" s="37" t="n"/>
-      <c r="D3" s="37" t="n"/>
+      <c r="C3" s="37" t="inlineStr">
+        <is>
+          <t>asfg</t>
+        </is>
+      </c>
+      <c r="D3" s="37" t="inlineStr">
+        <is>
+          <t>fnn</t>
+        </is>
+      </c>
       <c r="E3" s="28" t="inlineStr">
         <is>
           <t>aveo correa reparitcion 300 nequi 40 efecitvo</t>
@@ -1069,7 +1085,11 @@
       <c r="B4" s="36" t="n">
         <v>45236</v>
       </c>
-      <c r="C4" s="37" t="n"/>
+      <c r="C4" s="37" t="inlineStr">
+        <is>
+          <t>sdg</t>
+        </is>
+      </c>
       <c r="D4" s="37" t="n"/>
       <c r="E4" s="28" t="inlineStr">
         <is>

--- a/assets/contabilizacion.xlsx
+++ b/assets/contabilizacion.xlsx
@@ -1129,7 +1129,11 @@
         <v>45236</v>
       </c>
       <c r="C5" s="37" t="n"/>
-      <c r="D5" s="37" t="n"/>
+      <c r="D5" s="37" t="inlineStr">
+        <is>
+          <t>shdjfh</t>
+        </is>
+      </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
           <t>pila gasolina 30 angel y 70 pila  nequi juan</t>
@@ -1169,7 +1173,11 @@
       <c r="B6" s="36" t="n">
         <v>45236</v>
       </c>
-      <c r="C6" s="37" t="n"/>
+      <c r="C6" s="37" t="inlineStr">
+        <is>
+          <t>wueye</t>
+        </is>
+      </c>
       <c r="D6" s="37" t="n"/>
       <c r="E6" s="28" t="inlineStr">
         <is>

--- a/assets/contabilizacion.xlsx
+++ b/assets/contabilizacion.xlsx
@@ -985,7 +985,11 @@
       </c>
     </row>
     <row r="2" ht="19.5" customHeight="1">
-      <c r="A2" s="36" t="n"/>
+      <c r="A2" s="36" t="inlineStr">
+        <is>
+          <t>hola</t>
+        </is>
+      </c>
       <c r="B2" s="36" t="n">
         <v>45236</v>
       </c>

--- a/assets/contabilizacion.xlsx
+++ b/assets/contabilizacion.xlsx
@@ -840,12 +840,12 @@
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="28" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>prueba</t>
         </is>
       </c>
       <c r="B1" s="34" t="inlineStr">
         <is>
-          <t>Fecha</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="C1" s="28" t="inlineStr">
@@ -985,19 +985,13 @@
       </c>
     </row>
     <row r="2" ht="19.5" customHeight="1">
-      <c r="A2" s="36" t="inlineStr">
-        <is>
-          <t>hola</t>
-        </is>
-      </c>
-      <c r="B2" s="36" t="n">
-        <v>45236</v>
-      </c>
-      <c r="C2" s="37" t="inlineStr">
-        <is>
-          <t>nnnn</t>
-        </is>
-      </c>
+      <c r="A2" s="36" t="n"/>
+      <c r="B2" s="36" t="inlineStr">
+        <is>
+          <t>2023-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="C2" s="37" t="n"/>
       <c r="D2" s="37" t="inlineStr">
         <is>
           <t>21244</t>
@@ -1042,7 +1036,7 @@
       </c>
       <c r="C3" s="37" t="inlineStr">
         <is>
-          <t>asfg</t>
+          <t>65</t>
         </is>
       </c>
       <c r="D3" s="37" t="inlineStr">

--- a/assets/contabilizacion.xlsx
+++ b/assets/contabilizacion.xlsx
@@ -985,7 +985,9 @@
       </c>
     </row>
     <row r="2" ht="19.5" customHeight="1">
-      <c r="A2" s="36" t="n"/>
+      <c r="A2" s="36" t="n">
+        <v>235</v>
+      </c>
       <c r="B2" s="36" t="inlineStr">
         <is>
           <t>2023-11-06 00:00:00</t>
@@ -1030,7 +1032,9 @@
       <c r="AC2" s="38" t="n"/>
     </row>
     <row r="3" ht="19.5" customHeight="1">
-      <c r="A3" s="36" t="n"/>
+      <c r="A3" s="36" t="n">
+        <v>168</v>
+      </c>
       <c r="B3" s="36" t="n">
         <v>45236</v>
       </c>
@@ -1629,7 +1633,7 @@
     <row r="2" ht="18.75" customHeight="1">
       <c r="A2" s="18" t="inlineStr">
         <is>
-          <t>ch-38</t>
+          <t>ghgf</t>
         </is>
       </c>
       <c r="B2" s="28" t="inlineStr">
@@ -1654,33 +1658,21 @@
           <t>7e-z1</t>
         </is>
       </c>
-      <c r="H2" s="28">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,"Agotado",          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],"Menor al Mìnimo",    "Ok") )</f>
-        <v/>
-      </c>
-      <c r="I2" s="29">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,0,          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],1,    2) )</f>
-        <v/>
-      </c>
+      <c r="H2" s="28" t="n"/>
+      <c r="I2" s="29" t="n"/>
       <c r="J2" s="28" t="n"/>
-      <c r="K2" s="16">
-        <f>SUMIFS(Tabla5[cantidad],Tabla5[Codigo],Tabla3[[#This Row], [Codigo]])</f>
-        <v/>
-      </c>
+      <c r="K2" s="16" t="n"/>
       <c r="L2" s="30" t="inlineStr">
         <is>
           <t>ch-38</t>
         </is>
       </c>
-      <c r="M2" s="16">
-        <f>SUMIFS(Tabla3[EXISTENCIA ACTUAL],Tabla3[CODIGO UNITARIO],Tabla3[[#This Row], [CODIGO UNITARIO]])</f>
-        <v/>
-      </c>
+      <c r="M2" s="16" t="n"/>
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="18" t="inlineStr">
         <is>
-          <t>A-2862C</t>
+          <t>bvvc</t>
         </is>
       </c>
       <c r="B3" s="28" t="inlineStr">
@@ -1709,28 +1701,16 @@
           <t>7C-5</t>
         </is>
       </c>
-      <c r="H3" s="28">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,"Agotado",          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],"Menor al Mìnimo",    "Ok") )</f>
-        <v/>
-      </c>
-      <c r="I3" s="29">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,0,          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],1,    2) )</f>
-        <v/>
-      </c>
+      <c r="H3" s="28" t="n"/>
+      <c r="I3" s="29" t="n"/>
       <c r="J3" s="28" t="n"/>
-      <c r="K3" s="16">
-        <f>SUMIFS(Tabla5[cantidad],Tabla5[Codigo],Tabla3[[#This Row], [Codigo]])</f>
-        <v/>
-      </c>
+      <c r="K3" s="16" t="n"/>
       <c r="L3" s="30" t="inlineStr">
         <is>
           <t>a-111</t>
         </is>
       </c>
-      <c r="M3" s="16">
-        <f>SUMIFS(Tabla3[EXISTENCIA ACTUAL],Tabla3[CODIGO UNITARIO],Tabla3[[#This Row], [CODIGO UNITARIO]])</f>
-        <v/>
-      </c>
+      <c r="M3" s="16" t="n"/>
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="16" t="n">
@@ -1762,26 +1742,14 @@
           <t>8D-7</t>
         </is>
       </c>
-      <c r="H4" s="28">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,"Agotado",          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],"Menor al Mìnimo",    "Ok") )</f>
-        <v/>
-      </c>
-      <c r="I4" s="29">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,0,          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],1,    2) )</f>
-        <v/>
-      </c>
+      <c r="H4" s="28" t="n"/>
+      <c r="I4" s="29" t="n"/>
       <c r="J4" s="28" t="n"/>
-      <c r="K4" s="16">
-        <f>SUMIFS(Tabla5[cantidad],Tabla5[Codigo],Tabla3[[#This Row], [Codigo]])</f>
-        <v/>
-      </c>
+      <c r="K4" s="16" t="n"/>
       <c r="L4" s="16" t="n">
         <v>7700273904</v>
       </c>
-      <c r="M4" s="16">
-        <f>SUMIFS(Tabla3[EXISTENCIA ACTUAL],Tabla3[CODIGO UNITARIO],Tabla3[[#This Row], [CODIGO UNITARIO]])</f>
-        <v/>
-      </c>
+      <c r="M4" s="16" t="n"/>
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="16" t="n">
@@ -1813,26 +1781,14 @@
           <t>8D-5</t>
         </is>
       </c>
-      <c r="H5" s="28">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,"Agotado",          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],"Menor al Mìnimo",    "Ok") )</f>
-        <v/>
-      </c>
-      <c r="I5" s="29">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,0,          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],1,    2) )</f>
-        <v/>
-      </c>
+      <c r="H5" s="28" t="n"/>
+      <c r="I5" s="29" t="n"/>
       <c r="J5" s="28" t="n"/>
-      <c r="K5" s="16">
-        <f>SUMIFS(Tabla5[cantidad],Tabla5[Codigo],Tabla3[[#This Row], [Codigo]])</f>
-        <v/>
-      </c>
+      <c r="K5" s="16" t="n"/>
       <c r="L5" s="16" t="n">
         <v>8200141457</v>
       </c>
-      <c r="M5" s="16">
-        <f>SUMIFS(Tabla3[EXISTENCIA ACTUAL],Tabla3[CODIGO UNITARIO],Tabla3[[#This Row], [CODIGO UNITARIO]])</f>
-        <v/>
-      </c>
+      <c r="M5" s="16" t="n"/>
     </row>
     <row r="6" ht="18.75" customHeight="1">
       <c r="A6" s="18" t="inlineStr">
@@ -1866,28 +1822,16 @@
           <t>7D-1</t>
         </is>
       </c>
-      <c r="H6" s="28">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,"Agotado",          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],"Menor al Mìnimo",    "Ok") )</f>
-        <v/>
-      </c>
-      <c r="I6" s="29">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,0,          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],1,    2) )</f>
-        <v/>
-      </c>
+      <c r="H6" s="28" t="n"/>
+      <c r="I6" s="29" t="n"/>
       <c r="J6" s="28" t="n"/>
-      <c r="K6" s="16">
-        <f>SUMIFS(Tabla5[cantidad],Tabla5[Codigo],Tabla3[[#This Row], [Codigo]])</f>
-        <v/>
-      </c>
+      <c r="K6" s="16" t="n"/>
       <c r="L6" s="30" t="inlineStr">
         <is>
           <t>of-1402</t>
         </is>
       </c>
-      <c r="M6" s="16">
-        <f>SUMIFS(Tabla3[EXISTENCIA ACTUAL],Tabla3[CODIGO UNITARIO],Tabla3[[#This Row], [CODIGO UNITARIO]])</f>
-        <v/>
-      </c>
+      <c r="M6" s="16" t="n"/>
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="18" t="inlineStr">
@@ -1921,28 +1865,16 @@
           <t>13d</t>
         </is>
       </c>
-      <c r="H7" s="28">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,"Agotado",          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],"Menor al Mìnimo",    "Ok") )</f>
-        <v/>
-      </c>
-      <c r="I7" s="31">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,0,          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],1,    2) )</f>
-        <v/>
-      </c>
+      <c r="H7" s="28" t="n"/>
+      <c r="I7" s="31" t="n"/>
       <c r="J7" s="28" t="n"/>
-      <c r="K7" s="16">
-        <f>SUMIFS(Tabla5[cantidad],Tabla5[Codigo],Tabla3[[#This Row], [Codigo]])</f>
-        <v/>
-      </c>
+      <c r="K7" s="16" t="n"/>
       <c r="L7" s="30" t="inlineStr">
         <is>
           <t>valv</t>
         </is>
       </c>
-      <c r="M7" s="16">
-        <f>SUMIFS(Tabla3[EXISTENCIA ACTUAL],Tabla3[CODIGO UNITARIO],Tabla3[[#This Row], [CODIGO UNITARIO]])</f>
-        <v/>
-      </c>
+      <c r="M7" s="16" t="n"/>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="18" t="inlineStr">
@@ -1974,28 +1906,16 @@
           <t>9C-FINAL</t>
         </is>
       </c>
-      <c r="H8" s="28">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,"Agotado",          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],"Menor al Mìnimo",    "Ok") )</f>
-        <v/>
-      </c>
-      <c r="I8" s="31">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,0,          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],1,    2) )</f>
-        <v/>
-      </c>
+      <c r="H8" s="28" t="n"/>
+      <c r="I8" s="31" t="n"/>
       <c r="J8" s="28" t="n"/>
-      <c r="K8" s="16">
-        <f>SUMIFS(Tabla5[cantidad],Tabla5[Codigo],Tabla3[[#This Row], [Codigo]])</f>
-        <v/>
-      </c>
+      <c r="K8" s="16" t="n"/>
       <c r="L8" s="30" t="inlineStr">
         <is>
           <t>(09189</t>
         </is>
       </c>
-      <c r="M8" s="16">
-        <f>SUMIFS(Tabla3[EXISTENCIA ACTUAL],Tabla3[CODIGO UNITARIO],Tabla3[[#This Row], [CODIGO UNITARIO]])</f>
-        <v/>
-      </c>
+      <c r="M8" s="16" t="n"/>
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="18" t="inlineStr">
@@ -2029,28 +1949,16 @@
           <t>4C-3</t>
         </is>
       </c>
-      <c r="H9" s="28">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,"Agotado",          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],"Menor al Mìnimo",    "Ok") )</f>
-        <v/>
-      </c>
-      <c r="I9" s="31">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,0,          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],1,    2) )</f>
-        <v/>
-      </c>
+      <c r="H9" s="28" t="n"/>
+      <c r="I9" s="31" t="n"/>
       <c r="J9" s="28" t="n"/>
-      <c r="K9" s="16">
-        <f>SUMIFS(Tabla5[cantidad],Tabla5[Codigo],Tabla3[[#This Row], [Codigo]])</f>
-        <v/>
-      </c>
+      <c r="K9" s="16" t="n"/>
       <c r="L9" s="30" t="inlineStr">
         <is>
           <t>KOS-7412</t>
         </is>
       </c>
-      <c r="M9" s="16">
-        <f>SUMIFS(Tabla3[EXISTENCIA ACTUAL],Tabla3[CODIGO UNITARIO],Tabla3[[#This Row], [CODIGO UNITARIO]])</f>
-        <v/>
-      </c>
+      <c r="M9" s="16" t="n"/>
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="18" t="inlineStr">
@@ -2084,28 +1992,16 @@
           <t>7C-3</t>
         </is>
       </c>
-      <c r="H10" s="28">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,"Agotado",          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],"Menor al Mìnimo",    "Ok") )</f>
-        <v/>
-      </c>
-      <c r="I10" s="31">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,0,          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],1,    2) )</f>
-        <v/>
-      </c>
+      <c r="H10" s="28" t="n"/>
+      <c r="I10" s="31" t="n"/>
       <c r="J10" s="28" t="n"/>
-      <c r="K10" s="16">
-        <f>SUMIFS(Tabla5[cantidad],Tabla5[Codigo],Tabla3[[#This Row], [Codigo]])</f>
-        <v/>
-      </c>
+      <c r="K10" s="16" t="n"/>
       <c r="L10" s="30" t="inlineStr">
         <is>
           <t>a-14476</t>
         </is>
       </c>
-      <c r="M10" s="16">
-        <f>SUMIFS(Tabla3[EXISTENCIA ACTUAL],Tabla3[CODIGO UNITARIO],Tabla3[[#This Row], [CODIGO UNITARIO]])</f>
-        <v/>
-      </c>
+      <c r="M10" s="16" t="n"/>
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="18" t="inlineStr">
@@ -2139,28 +2035,16 @@
           <t>7C-4</t>
         </is>
       </c>
-      <c r="H11" s="28">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,"Agotado",          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],"Menor al Mìnimo",    "Ok") )</f>
-        <v/>
-      </c>
-      <c r="I11" s="31">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,0,          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],1,    2) )</f>
-        <v/>
-      </c>
+      <c r="H11" s="28" t="n"/>
+      <c r="I11" s="31" t="n"/>
       <c r="J11" s="28" t="n"/>
-      <c r="K11" s="16">
-        <f>SUMIFS(Tabla5[cantidad],Tabla5[Codigo],Tabla3[[#This Row], [Codigo]])</f>
-        <v/>
-      </c>
+      <c r="K11" s="16" t="n"/>
       <c r="L11" s="30" t="inlineStr">
         <is>
           <t>a-323</t>
         </is>
       </c>
-      <c r="M11" s="16">
-        <f>SUMIFS(Tabla3[EXISTENCIA ACTUAL],Tabla3[CODIGO UNITARIO],Tabla3[[#This Row], [CODIGO UNITARIO]])</f>
-        <v/>
-      </c>
+      <c r="M11" s="16" t="n"/>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="18" t="inlineStr">
@@ -2194,28 +2078,16 @@
           <t>7C-5</t>
         </is>
       </c>
-      <c r="H12" s="28">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,"Agotado",          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],"Menor al Mìnimo",    "Ok") )</f>
-        <v/>
-      </c>
-      <c r="I12" s="31">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,0,          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],1,    2) )</f>
-        <v/>
-      </c>
+      <c r="H12" s="28" t="n"/>
+      <c r="I12" s="31" t="n"/>
       <c r="J12" s="28" t="n"/>
-      <c r="K12" s="16">
-        <f>SUMIFS(Tabla5[cantidad],Tabla5[Codigo],Tabla3[[#This Row], [Codigo]])</f>
-        <v/>
-      </c>
+      <c r="K12" s="16" t="n"/>
       <c r="L12" s="30" t="inlineStr">
         <is>
           <t>a-111</t>
         </is>
       </c>
-      <c r="M12" s="16">
-        <f>SUMIFS(Tabla3[EXISTENCIA ACTUAL],Tabla3[CODIGO UNITARIO],Tabla3[[#This Row], [CODIGO UNITARIO]])</f>
-        <v/>
-      </c>
+      <c r="M12" s="16" t="n"/>
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="18" t="inlineStr">
@@ -2249,28 +2121,16 @@
           <t>7C-6</t>
         </is>
       </c>
-      <c r="H13" s="28">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,"Agotado",          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],"Menor al Mìnimo",    "Ok") )</f>
-        <v/>
-      </c>
-      <c r="I13" s="31">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,0,          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],1,    2) )</f>
-        <v/>
-      </c>
+      <c r="H13" s="28" t="n"/>
+      <c r="I13" s="31" t="n"/>
       <c r="J13" s="28" t="n"/>
-      <c r="K13" s="16">
-        <f>SUMIFS(Tabla5[cantidad],Tabla5[Codigo],Tabla3[[#This Row], [Codigo]])</f>
-        <v/>
-      </c>
+      <c r="K13" s="16" t="n"/>
       <c r="L13" s="30" t="inlineStr">
         <is>
           <t>a-3603</t>
         </is>
       </c>
-      <c r="M13" s="16">
-        <f>SUMIFS(Tabla3[EXISTENCIA ACTUAL],Tabla3[CODIGO UNITARIO],Tabla3[[#This Row], [CODIGO UNITARIO]])</f>
-        <v/>
-      </c>
+      <c r="M13" s="16" t="n"/>
     </row>
     <row r="14" ht="18.75" customHeight="1">
       <c r="A14" s="18" t="inlineStr">
@@ -2304,28 +2164,16 @@
           <t>4a</t>
         </is>
       </c>
-      <c r="H14" s="28">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,"Agotado",          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],"Menor al Mìnimo",    "Ok") )</f>
-        <v/>
-      </c>
-      <c r="I14" s="29">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,0,          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],1,    2) )</f>
-        <v/>
-      </c>
+      <c r="H14" s="28" t="n"/>
+      <c r="I14" s="29" t="n"/>
       <c r="J14" s="28" t="n"/>
-      <c r="K14" s="16">
-        <f>SUMIFS(Tabla5[cantidad],Tabla5[Codigo],Tabla3[[#This Row], [Codigo]])</f>
-        <v/>
-      </c>
+      <c r="K14" s="16" t="n"/>
       <c r="L14" s="30" t="inlineStr">
         <is>
           <t>valv</t>
         </is>
       </c>
-      <c r="M14" s="16">
-        <f>SUMIFS(Tabla3[EXISTENCIA ACTUAL],Tabla3[CODIGO UNITARIO],Tabla3[[#This Row], [CODIGO UNITARIO]])</f>
-        <v/>
-      </c>
+      <c r="M14" s="16" t="n"/>
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="18" t="inlineStr">
@@ -2359,28 +2207,16 @@
           <t>bolsa pcv/ 12c-b3</t>
         </is>
       </c>
-      <c r="H15" s="28">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,"Agotado",          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],"Menor al Mìnimo",    "Ok") )</f>
-        <v/>
-      </c>
-      <c r="I15" s="29">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,0,          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],1,    2) )</f>
-        <v/>
-      </c>
+      <c r="H15" s="28" t="n"/>
+      <c r="I15" s="29" t="n"/>
       <c r="J15" s="28" t="n"/>
-      <c r="K15" s="16">
-        <f>SUMIFS(Tabla5[cantidad],Tabla5[Codigo],Tabla3[[#This Row], [Codigo]])</f>
-        <v/>
-      </c>
+      <c r="K15" s="16" t="n"/>
       <c r="L15" s="30" t="inlineStr">
         <is>
           <t>pcvaveo</t>
         </is>
       </c>
-      <c r="M15" s="16">
-        <f>SUMIFS(Tabla3[EXISTENCIA ACTUAL],Tabla3[CODIGO UNITARIO],Tabla3[[#This Row], [CODIGO UNITARIO]])</f>
-        <v/>
-      </c>
+      <c r="M15" s="16" t="n"/>
     </row>
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="18" t="inlineStr">
@@ -2414,28 +2250,16 @@
           <t>bolsa pcv/ 12c-b3</t>
         </is>
       </c>
-      <c r="H16" s="28">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,"Agotado",          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],"Menor al Mìnimo",    "Ok") )</f>
-        <v/>
-      </c>
-      <c r="I16" s="29">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,0,          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],1,    2) )</f>
-        <v/>
-      </c>
+      <c r="H16" s="28" t="n"/>
+      <c r="I16" s="29" t="n"/>
       <c r="J16" s="28" t="n"/>
-      <c r="K16" s="16">
-        <f>SUMIFS(Tabla5[cantidad],Tabla5[Codigo],Tabla3[[#This Row], [Codigo]])</f>
-        <v/>
-      </c>
+      <c r="K16" s="16" t="n"/>
       <c r="L16" s="32" t="inlineStr">
         <is>
           <t>18118</t>
         </is>
       </c>
-      <c r="M16" s="16">
-        <f>SUMIFS(Tabla3[EXISTENCIA ACTUAL],Tabla3[CODIGO UNITARIO],Tabla3[[#This Row], [CODIGO UNITARIO]])</f>
-        <v/>
-      </c>
+      <c r="M16" s="16" t="n"/>
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="16" t="n">
@@ -2467,28 +2291,16 @@
           <t>bolsa pcv/ 12c-b3</t>
         </is>
       </c>
-      <c r="H17" s="28">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,"Agotado",          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],"Menor al Mìnimo",    "Ok") )</f>
-        <v/>
-      </c>
-      <c r="I17" s="29">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,0,          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],1,    2) )</f>
-        <v/>
-      </c>
+      <c r="H17" s="28" t="n"/>
+      <c r="I17" s="29" t="n"/>
       <c r="J17" s="28" t="n"/>
-      <c r="K17" s="16">
-        <f>SUMIFS(Tabla5[cantidad],Tabla5[Codigo],Tabla3[[#This Row], [Codigo]])</f>
-        <v/>
-      </c>
+      <c r="K17" s="16" t="n"/>
       <c r="L17" s="32" t="inlineStr">
         <is>
           <t>96991801</t>
         </is>
       </c>
-      <c r="M17" s="16">
-        <f>SUMIFS(Tabla3[EXISTENCIA ACTUAL],Tabla3[CODIGO UNITARIO],Tabla3[[#This Row], [CODIGO UNITARIO]])</f>
-        <v/>
-      </c>
+      <c r="M17" s="16" t="n"/>
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="16" t="n">
@@ -2520,28 +2332,16 @@
           <t>bolsa pcv/ 12c-b3</t>
         </is>
       </c>
-      <c r="H18" s="28">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,"Agotado",          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],"Menor al Mìnimo",    "Ok") )</f>
-        <v/>
-      </c>
-      <c r="I18" s="29">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,0,          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],1,    2) )</f>
-        <v/>
-      </c>
+      <c r="H18" s="28" t="n"/>
+      <c r="I18" s="29" t="n"/>
       <c r="J18" s="28" t="n"/>
-      <c r="K18" s="16">
-        <f>SUMIFS(Tabla5[cantidad],Tabla5[Codigo],Tabla3[[#This Row], [Codigo]])</f>
-        <v/>
-      </c>
+      <c r="K18" s="16" t="n"/>
       <c r="L18" s="32" t="inlineStr">
         <is>
           <t>18118</t>
         </is>
       </c>
-      <c r="M18" s="16">
-        <f>SUMIFS(Tabla3[EXISTENCIA ACTUAL],Tabla3[CODIGO UNITARIO],Tabla3[[#This Row], [CODIGO UNITARIO]])</f>
-        <v/>
-      </c>
+      <c r="M18" s="16" t="n"/>
     </row>
     <row r="19" ht="18.75" customHeight="1">
       <c r="A19" s="18" t="inlineStr">
@@ -2575,28 +2375,16 @@
           <t>8C-2</t>
         </is>
       </c>
-      <c r="H19" s="28">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,"Agotado",          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],"Menor al Mìnimo",    "Ok") )</f>
-        <v/>
-      </c>
-      <c r="I19" s="29">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,0,          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],1,    2) )</f>
-        <v/>
-      </c>
+      <c r="H19" s="28" t="n"/>
+      <c r="I19" s="29" t="n"/>
       <c r="J19" s="28" t="n"/>
-      <c r="K19" s="16">
-        <f>SUMIFS(Tabla5[cantidad],Tabla5[Codigo],Tabla3[[#This Row], [Codigo]])</f>
-        <v/>
-      </c>
+      <c r="K19" s="16" t="n"/>
       <c r="L19" s="30" t="inlineStr">
         <is>
           <t>2-01-0239</t>
         </is>
       </c>
-      <c r="M19" s="16">
-        <f>SUMIFS(Tabla3[EXISTENCIA ACTUAL],Tabla3[CODIGO UNITARIO],Tabla3[[#This Row], [CODIGO UNITARIO]])</f>
-        <v/>
-      </c>
+      <c r="M19" s="16" t="n"/>
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="18" t="inlineStr">
@@ -2630,26 +2418,14 @@
           <t>bolsa pcv/ 12c-b3</t>
         </is>
       </c>
-      <c r="H20" s="28">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,"Agotado",          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],"Menor al Mìnimo",    "Ok") )</f>
-        <v/>
-      </c>
-      <c r="I20" s="29">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,0,          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],1,    2) )</f>
-        <v/>
-      </c>
+      <c r="H20" s="28" t="n"/>
+      <c r="I20" s="29" t="n"/>
       <c r="J20" s="28" t="n"/>
-      <c r="K20" s="16">
-        <f>SUMIFS(Tabla5[cantidad],Tabla5[Codigo],Tabla3[[#This Row], [Codigo]])</f>
-        <v/>
-      </c>
+      <c r="K20" s="16" t="n"/>
       <c r="L20" s="16" t="n">
         <v>14320</v>
       </c>
-      <c r="M20" s="16">
-        <f>SUMIFS(Tabla3[EXISTENCIA ACTUAL],Tabla3[CODIGO UNITARIO],Tabla3[[#This Row], [CODIGO UNITARIO]])</f>
-        <v/>
-      </c>
+      <c r="M20" s="16" t="n"/>
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="A21" s="16" t="n">
@@ -2681,26 +2457,14 @@
           <t>bolsa pcv/ 12c-b3</t>
         </is>
       </c>
-      <c r="H21" s="28">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,"Agotado",          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],"Menor al Mìnimo",    "Ok") )</f>
-        <v/>
-      </c>
-      <c r="I21" s="29">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,0,          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],1,    2) )</f>
-        <v/>
-      </c>
+      <c r="H21" s="28" t="n"/>
+      <c r="I21" s="29" t="n"/>
       <c r="J21" s="28" t="n"/>
-      <c r="K21" s="16">
-        <f>SUMIFS(Tabla5[cantidad],Tabla5[Codigo],Tabla3[[#This Row], [Codigo]])</f>
-        <v/>
-      </c>
+      <c r="K21" s="16" t="n"/>
       <c r="L21" s="16" t="n">
         <v>24516476</v>
       </c>
-      <c r="M21" s="16">
-        <f>SUMIFS(Tabla3[EXISTENCIA ACTUAL],Tabla3[CODIGO UNITARIO],Tabla3[[#This Row], [CODIGO UNITARIO]])</f>
-        <v/>
-      </c>
+      <c r="M21" s="16" t="n"/>
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="16" t="n">
@@ -2732,26 +2496,14 @@
           <t>2a-4</t>
         </is>
       </c>
-      <c r="H22" s="28">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,"Agotado",          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],"Menor al Mìnimo",    "Ok") )</f>
-        <v/>
-      </c>
-      <c r="I22" s="29">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,0,          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],1,    2) )</f>
-        <v/>
-      </c>
+      <c r="H22" s="28" t="n"/>
+      <c r="I22" s="29" t="n"/>
       <c r="J22" s="28" t="n"/>
-      <c r="K22" s="16">
-        <f>SUMIFS(Tabla5[cantidad],Tabla5[Codigo],Tabla3[[#This Row], [Codigo]])</f>
-        <v/>
-      </c>
+      <c r="K22" s="16" t="n"/>
       <c r="L22" s="16" t="n">
         <v>96535300</v>
       </c>
-      <c r="M22" s="16">
-        <f>SUMIFS(Tabla3[EXISTENCIA ACTUAL],Tabla3[CODIGO UNITARIO],Tabla3[[#This Row], [CODIGO UNITARIO]])</f>
-        <v/>
-      </c>
+      <c r="M22" s="16" t="n"/>
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" s="18" t="inlineStr">
@@ -2781,28 +2533,16 @@
           <t>bolsa pcv/ 12c-b3</t>
         </is>
       </c>
-      <c r="H23" s="28">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,"Agotado",          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],"Menor al Mìnimo",    "Ok") )</f>
-        <v/>
-      </c>
-      <c r="I23" s="31">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,0,          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],1,    2) )</f>
-        <v/>
-      </c>
+      <c r="H23" s="28" t="n"/>
+      <c r="I23" s="31" t="n"/>
       <c r="J23" s="28" t="n"/>
-      <c r="K23" s="16">
-        <f>SUMIFS(Tabla5[cantidad],Tabla5[Codigo],Tabla3[[#This Row], [Codigo]])</f>
-        <v/>
-      </c>
+      <c r="K23" s="16" t="n"/>
       <c r="L23" s="30" t="inlineStr">
         <is>
           <t>pcvaveo</t>
         </is>
       </c>
-      <c r="M23" s="16">
-        <f>SUMIFS(Tabla3[EXISTENCIA ACTUAL],Tabla3[CODIGO UNITARIO],Tabla3[[#This Row], [CODIGO UNITARIO]])</f>
-        <v/>
-      </c>
+      <c r="M23" s="16" t="n"/>
     </row>
     <row r="24" ht="18.75" customHeight="1">
       <c r="A24" s="18" t="inlineStr">
@@ -2834,28 +2574,16 @@
           <t>bolsa pcv/ 12c-b3</t>
         </is>
       </c>
-      <c r="H24" s="28">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,"Agotado",          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],"Menor al Mìnimo",    "Ok") )</f>
-        <v/>
-      </c>
-      <c r="I24" s="31">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,0,          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],1,    2) )</f>
-        <v/>
-      </c>
+      <c r="H24" s="28" t="n"/>
+      <c r="I24" s="31" t="n"/>
       <c r="J24" s="28" t="n"/>
-      <c r="K24" s="16">
-        <f>SUMIFS(Tabla5[cantidad],Tabla5[Codigo],Tabla3[[#This Row], [Codigo]])</f>
-        <v/>
-      </c>
+      <c r="K24" s="16" t="n"/>
       <c r="L24" s="32" t="inlineStr">
         <is>
           <t>18118</t>
         </is>
       </c>
-      <c r="M24" s="16">
-        <f>SUMIFS(Tabla3[EXISTENCIA ACTUAL],Tabla3[CODIGO UNITARIO],Tabla3[[#This Row], [CODIGO UNITARIO]])</f>
-        <v/>
-      </c>
+      <c r="M24" s="16" t="n"/>
     </row>
     <row r="25" ht="18.75" customHeight="1">
       <c r="A25" s="18" t="inlineStr">
@@ -2887,28 +2615,16 @@
           <t>1A-3</t>
         </is>
       </c>
-      <c r="H25" s="28">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,"Agotado",          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],"Menor al Mìnimo",    "Ok") )</f>
-        <v/>
-      </c>
-      <c r="I25" s="29">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,0,          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],1,    2) )</f>
-        <v/>
-      </c>
+      <c r="H25" s="28" t="n"/>
+      <c r="I25" s="29" t="n"/>
       <c r="J25" s="28" t="n"/>
-      <c r="K25" s="16">
-        <f>SUMIFS(Tabla5[cantidad],Tabla5[Codigo],Tabla3[[#This Row], [Codigo]])</f>
-        <v/>
-      </c>
+      <c r="K25" s="16" t="n"/>
       <c r="L25" s="30" t="inlineStr">
         <is>
           <t>CCX008</t>
         </is>
       </c>
-      <c r="M25" s="16">
-        <f>SUMIFS(Tabla3[EXISTENCIA ACTUAL],Tabla3[CODIGO UNITARIO],Tabla3[[#This Row], [CODIGO UNITARIO]])</f>
-        <v/>
-      </c>
+      <c r="M25" s="16" t="n"/>
     </row>
     <row r="26" ht="18.75" customHeight="1">
       <c r="A26" s="16" t="n">
@@ -2940,26 +2656,14 @@
           <t>bolsa pcv/ 12c-b3</t>
         </is>
       </c>
-      <c r="H26" s="28">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,"Agotado",          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],"Menor al Mìnimo",    "Ok") )</f>
-        <v/>
-      </c>
-      <c r="I26" s="31">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,0,          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],1,    2) )</f>
-        <v/>
-      </c>
+      <c r="H26" s="28" t="n"/>
+      <c r="I26" s="31" t="n"/>
       <c r="J26" s="28" t="n"/>
-      <c r="K26" s="16">
-        <f>SUMIFS(Tabla5[cantidad],Tabla5[Codigo],Tabla3[[#This Row], [Codigo]])</f>
-        <v/>
-      </c>
+      <c r="K26" s="16" t="n"/>
       <c r="L26" s="16" t="n">
         <v>14320</v>
       </c>
-      <c r="M26" s="16">
-        <f>SUMIFS(Tabla3[EXISTENCIA ACTUAL],Tabla3[CODIGO UNITARIO],Tabla3[[#This Row], [CODIGO UNITARIO]])</f>
-        <v/>
-      </c>
+      <c r="M26" s="16" t="n"/>
     </row>
     <row r="27" ht="18.75" customHeight="1">
       <c r="A27" s="18" t="inlineStr">
@@ -2993,28 +2697,16 @@
           <t>bolsa pcv/ 12c-b3</t>
         </is>
       </c>
-      <c r="H27" s="28">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,"Agotado",          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],"Menor al Mìnimo",    "Ok") )</f>
-        <v/>
-      </c>
-      <c r="I27" s="31">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,0,          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],1,    2) )</f>
-        <v/>
-      </c>
+      <c r="H27" s="28" t="n"/>
+      <c r="I27" s="31" t="n"/>
       <c r="J27" s="28" t="n"/>
-      <c r="K27" s="16">
-        <f>SUMIFS(Tabla5[cantidad],Tabla5[Codigo],Tabla3[[#This Row], [Codigo]])</f>
-        <v/>
-      </c>
+      <c r="K27" s="16" t="n"/>
       <c r="L27" s="30" t="inlineStr">
         <is>
           <t>pcvaveo</t>
         </is>
       </c>
-      <c r="M27" s="16">
-        <f>SUMIFS(Tabla3[EXISTENCIA ACTUAL],Tabla3[CODIGO UNITARIO],Tabla3[[#This Row], [CODIGO UNITARIO]])</f>
-        <v/>
-      </c>
+      <c r="M27" s="16" t="n"/>
     </row>
     <row r="28" ht="18.75" customHeight="1">
       <c r="A28" s="18" t="inlineStr">
@@ -3048,28 +2740,16 @@
           <t>1A-1</t>
         </is>
       </c>
-      <c r="H28" s="28">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,"Agotado",          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],"Menor al Mìnimo",    "Ok") )</f>
-        <v/>
-      </c>
-      <c r="I28" s="29">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,0,          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],1,    2) )</f>
-        <v/>
-      </c>
+      <c r="H28" s="28" t="n"/>
+      <c r="I28" s="29" t="n"/>
       <c r="J28" s="28" t="n"/>
-      <c r="K28" s="16">
-        <f>SUMIFS(Tabla5[cantidad],Tabla5[Codigo],Tabla3[[#This Row], [Codigo]])</f>
-        <v/>
-      </c>
+      <c r="K28" s="16" t="n"/>
       <c r="L28" s="30" t="inlineStr">
         <is>
           <t>kre-3010</t>
         </is>
       </c>
-      <c r="M28" s="16">
-        <f>SUMIFS(Tabla3[EXISTENCIA ACTUAL],Tabla3[CODIGO UNITARIO],Tabla3[[#This Row], [CODIGO UNITARIO]])</f>
-        <v/>
-      </c>
+      <c r="M28" s="16" t="n"/>
     </row>
     <row r="29" ht="18.75" customHeight="1">
       <c r="A29" s="18" t="inlineStr">
@@ -3099,28 +2779,16 @@
           <t>bolsa pcv/ 12c-b3</t>
         </is>
       </c>
-      <c r="H29" s="28">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,"Agotado",          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],"Menor al Mìnimo",    "Ok") )</f>
-        <v/>
-      </c>
-      <c r="I29" s="31">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,0,          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],1,    2) )</f>
-        <v/>
-      </c>
+      <c r="H29" s="28" t="n"/>
+      <c r="I29" s="31" t="n"/>
       <c r="J29" s="28" t="n"/>
-      <c r="K29" s="16">
-        <f>SUMIFS(Tabla5[cantidad],Tabla5[Codigo],Tabla3[[#This Row], [Codigo]])</f>
-        <v/>
-      </c>
+      <c r="K29" s="16" t="n"/>
       <c r="L29" s="30" t="inlineStr">
         <is>
           <t>sailpcv</t>
         </is>
       </c>
-      <c r="M29" s="16">
-        <f>SUMIFS(Tabla3[EXISTENCIA ACTUAL],Tabla3[CODIGO UNITARIO],Tabla3[[#This Row], [CODIGO UNITARIO]])</f>
-        <v/>
-      </c>
+      <c r="M29" s="16" t="n"/>
     </row>
     <row r="30" ht="18.75" customHeight="1">
       <c r="A30" s="16" t="n">
@@ -3150,28 +2818,16 @@
           <t>bolsa pcv/ 12c-b3</t>
         </is>
       </c>
-      <c r="H30" s="28">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,"Agotado",          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],"Menor al Mìnimo",    "Ok") )</f>
-        <v/>
-      </c>
-      <c r="I30" s="31">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,0,          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],1,    2) )</f>
-        <v/>
-      </c>
+      <c r="H30" s="28" t="n"/>
+      <c r="I30" s="31" t="n"/>
       <c r="J30" s="28" t="n"/>
-      <c r="K30" s="16">
-        <f>SUMIFS(Tabla5[cantidad],Tabla5[Codigo],Tabla3[[#This Row], [Codigo]])</f>
-        <v/>
-      </c>
+      <c r="K30" s="16" t="n"/>
       <c r="L30" s="30" t="inlineStr">
         <is>
           <t>pcvaveo</t>
         </is>
       </c>
-      <c r="M30" s="16">
-        <f>SUMIFS(Tabla3[EXISTENCIA ACTUAL],Tabla3[CODIGO UNITARIO],Tabla3[[#This Row], [CODIGO UNITARIO]])</f>
-        <v/>
-      </c>
+      <c r="M30" s="16" t="n"/>
     </row>
     <row r="31" ht="18.75" customHeight="1">
       <c r="A31" s="16" t="n">
@@ -3197,26 +2853,14 @@
         </is>
       </c>
       <c r="G31" s="28" t="n"/>
-      <c r="H31" s="28">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,"Agotado",          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],"Menor al Mìnimo",    "Ok") )</f>
-        <v/>
-      </c>
-      <c r="I31" s="31">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,0,          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],1,    2) )</f>
-        <v/>
-      </c>
+      <c r="H31" s="28" t="n"/>
+      <c r="I31" s="31" t="n"/>
       <c r="J31" s="28" t="n"/>
-      <c r="K31" s="16">
-        <f>SUMIFS(Tabla5[cantidad],Tabla5[Codigo],Tabla3[[#This Row], [Codigo]])</f>
-        <v/>
-      </c>
+      <c r="K31" s="16" t="n"/>
       <c r="L31" s="16" t="n">
         <v>94580183</v>
       </c>
-      <c r="M31" s="16">
-        <f>SUMIFS(Tabla3[EXISTENCIA ACTUAL],Tabla3[CODIGO UNITARIO],Tabla3[[#This Row], [CODIGO UNITARIO]])</f>
-        <v/>
-      </c>
+      <c r="M31" s="16" t="n"/>
     </row>
     <row r="32" ht="18.75" customHeight="1">
       <c r="A32" s="16" t="n">
@@ -3248,28 +2892,16 @@
           <t>11f-1a</t>
         </is>
       </c>
-      <c r="H32" s="28">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,"Agotado",          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],"Menor al Mìnimo",    "Ok") )</f>
-        <v/>
-      </c>
-      <c r="I32" s="29">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,0,          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],1,    2) )</f>
-        <v/>
-      </c>
+      <c r="H32" s="28" t="n"/>
+      <c r="I32" s="29" t="n"/>
       <c r="J32" s="28" t="n"/>
-      <c r="K32" s="16">
-        <f>SUMIFS(Tabla5[cantidad],Tabla5[Codigo],Tabla3[[#This Row], [Codigo]])</f>
-        <v/>
-      </c>
+      <c r="K32" s="16" t="n"/>
       <c r="L32" s="30" t="inlineStr">
         <is>
           <t>257-010</t>
         </is>
       </c>
-      <c r="M32" s="16">
-        <f>SUMIFS(Tabla3[EXISTENCIA ACTUAL],Tabla3[CODIGO UNITARIO],Tabla3[[#This Row], [CODIGO UNITARIO]])</f>
-        <v/>
-      </c>
+      <c r="M32" s="16" t="n"/>
     </row>
     <row r="33" ht="18.75" customHeight="1">
       <c r="A33" s="18" t="inlineStr">
@@ -3301,28 +2933,16 @@
           <t>11f-8a</t>
         </is>
       </c>
-      <c r="H33" s="28">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,"Agotado",          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],"Menor al Mìnimo",    "Ok") )</f>
-        <v/>
-      </c>
-      <c r="I33" s="29">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,0,          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],1,    2) )</f>
-        <v/>
-      </c>
+      <c r="H33" s="28" t="n"/>
+      <c r="I33" s="29" t="n"/>
       <c r="J33" s="28" t="n"/>
-      <c r="K33" s="16">
-        <f>SUMIFS(Tabla5[cantidad],Tabla5[Codigo],Tabla3[[#This Row], [Codigo]])</f>
-        <v/>
-      </c>
+      <c r="K33" s="16" t="n"/>
       <c r="L33" s="30" t="inlineStr">
         <is>
           <t>257-010</t>
         </is>
       </c>
-      <c r="M33" s="16">
-        <f>SUMIFS(Tabla3[EXISTENCIA ACTUAL],Tabla3[CODIGO UNITARIO],Tabla3[[#This Row], [CODIGO UNITARIO]])</f>
-        <v/>
-      </c>
+      <c r="M33" s="16" t="n"/>
     </row>
     <row r="34" ht="18.75" customHeight="1">
       <c r="A34" s="16" t="n">
@@ -3350,28 +2970,16 @@
         </is>
       </c>
       <c r="G34" s="28" t="n"/>
-      <c r="H34" s="28">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,"Agotado",          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],"Menor al Mìnimo",    "Ok") )</f>
-        <v/>
-      </c>
-      <c r="I34" s="29">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,0,          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],1,    2) )</f>
-        <v/>
-      </c>
+      <c r="H34" s="28" t="n"/>
+      <c r="I34" s="29" t="n"/>
       <c r="J34" s="28" t="n"/>
-      <c r="K34" s="16">
-        <f>SUMIFS(Tabla5[cantidad],Tabla5[Codigo],Tabla3[[#This Row], [Codigo]])</f>
-        <v/>
-      </c>
+      <c r="K34" s="16" t="n"/>
       <c r="L34" s="30" t="inlineStr">
         <is>
           <t>257-010</t>
         </is>
       </c>
-      <c r="M34" s="16">
-        <f>SUMIFS(Tabla3[EXISTENCIA ACTUAL],Tabla3[CODIGO UNITARIO],Tabla3[[#This Row], [CODIGO UNITARIO]])</f>
-        <v/>
-      </c>
+      <c r="M34" s="16" t="n"/>
     </row>
     <row r="35" ht="18.75" customHeight="1">
       <c r="A35" s="16" t="n">
@@ -3403,28 +3011,16 @@
           <t>4D-1</t>
         </is>
       </c>
-      <c r="H35" s="28">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,"Agotado",          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],"Menor al Mìnimo",    "Ok") )</f>
-        <v/>
-      </c>
-      <c r="I35" s="29">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,0,          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],1,    2) )</f>
-        <v/>
-      </c>
+      <c r="H35" s="28" t="n"/>
+      <c r="I35" s="29" t="n"/>
       <c r="J35" s="28" t="n"/>
-      <c r="K35" s="16">
-        <f>SUMIFS(Tabla5[cantidad],Tabla5[Codigo],Tabla3[[#This Row], [Codigo]])</f>
-        <v/>
-      </c>
+      <c r="K35" s="16" t="n"/>
       <c r="L35" s="32" t="inlineStr">
         <is>
           <t>87087</t>
         </is>
       </c>
-      <c r="M35" s="16">
-        <f>SUMIFS(Tabla3[EXISTENCIA ACTUAL],Tabla3[CODIGO UNITARIO],Tabla3[[#This Row], [CODIGO UNITARIO]])</f>
-        <v/>
-      </c>
+      <c r="M35" s="16" t="n"/>
     </row>
     <row r="36" ht="18.75" customHeight="1">
       <c r="A36" s="16" t="n">
@@ -3448,26 +3044,14 @@
           <t>7e-z1</t>
         </is>
       </c>
-      <c r="H36" s="28">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,"Agotado",          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],"Menor al Mìnimo",    "Ok") )</f>
-        <v/>
-      </c>
-      <c r="I36" s="29">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,0,          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],1,    2) )</f>
-        <v/>
-      </c>
+      <c r="H36" s="28" t="n"/>
+      <c r="I36" s="29" t="n"/>
       <c r="J36" s="28" t="n"/>
-      <c r="K36" s="16">
-        <f>SUMIFS(Tabla5[cantidad],Tabla5[Codigo],Tabla3[[#This Row], [Codigo]])</f>
-        <v/>
-      </c>
+      <c r="K36" s="16" t="n"/>
       <c r="L36" s="16" t="n">
         <v>770101229</v>
       </c>
-      <c r="M36" s="16">
-        <f>SUMIFS(Tabla3[EXISTENCIA ACTUAL],Tabla3[CODIGO UNITARIO],Tabla3[[#This Row], [CODIGO UNITARIO]])</f>
-        <v/>
-      </c>
+      <c r="M36" s="16" t="n"/>
     </row>
     <row r="37" ht="18.75" customHeight="1">
       <c r="A37" s="18" t="inlineStr">
@@ -3501,28 +3085,16 @@
           <t>1A-7</t>
         </is>
       </c>
-      <c r="H37" s="28">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,"Agotado",          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],"Menor al Mìnimo",    "Ok") )</f>
-        <v/>
-      </c>
-      <c r="I37" s="29">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,0,          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],1,    2) )</f>
-        <v/>
-      </c>
+      <c r="H37" s="28" t="n"/>
+      <c r="I37" s="29" t="n"/>
       <c r="J37" s="28" t="n"/>
-      <c r="K37" s="16">
-        <f>SUMIFS(Tabla5[cantidad],Tabla5[Codigo],Tabla3[[#This Row], [Codigo]])</f>
-        <v/>
-      </c>
+      <c r="K37" s="16" t="n"/>
       <c r="L37" s="30" t="inlineStr">
         <is>
           <t>kre-3016</t>
         </is>
       </c>
-      <c r="M37" s="16">
-        <f>SUMIFS(Tabla3[EXISTENCIA ACTUAL],Tabla3[CODIGO UNITARIO],Tabla3[[#This Row], [CODIGO UNITARIO]])</f>
-        <v/>
-      </c>
+      <c r="M37" s="16" t="n"/>
     </row>
     <row r="38" ht="18.75" customHeight="1">
       <c r="A38" s="16" t="n">
@@ -3544,26 +3116,14 @@
         </is>
       </c>
       <c r="G38" s="28" t="n"/>
-      <c r="H38" s="28">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,"Agotado",          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],"Menor al Mìnimo",    "Ok") )</f>
-        <v/>
-      </c>
-      <c r="I38" s="29">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,0,          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],1,    2) )</f>
-        <v/>
-      </c>
+      <c r="H38" s="28" t="n"/>
+      <c r="I38" s="29" t="n"/>
       <c r="J38" s="28" t="n"/>
-      <c r="K38" s="16">
-        <f>SUMIFS(Tabla5[cantidad],Tabla5[Codigo],Tabla3[[#This Row], [Codigo]])</f>
-        <v/>
-      </c>
+      <c r="K38" s="16" t="n"/>
       <c r="L38" s="16" t="n">
         <v>8200134513</v>
       </c>
-      <c r="M38" s="16">
-        <f>SUMIFS(Tabla3[EXISTENCIA ACTUAL],Tabla3[CODIGO UNITARIO],Tabla3[[#This Row], [CODIGO UNITARIO]])</f>
-        <v/>
-      </c>
+      <c r="M38" s="16" t="n"/>
     </row>
     <row r="39" ht="18.75" customHeight="1">
       <c r="A39" s="18" t="inlineStr">
@@ -3597,28 +3157,16 @@
           <t>7E-Z1</t>
         </is>
       </c>
-      <c r="H39" s="28">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,"Agotado",          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],"Menor al Mìnimo",    "Ok") )</f>
-        <v/>
-      </c>
-      <c r="I39" s="31">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,0,          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],1,    2) )</f>
-        <v/>
-      </c>
+      <c r="H39" s="28" t="n"/>
+      <c r="I39" s="31" t="n"/>
       <c r="J39" s="28" t="n"/>
-      <c r="K39" s="16">
-        <f>SUMIFS(Tabla5[cantidad],Tabla5[Codigo],Tabla3[[#This Row], [Codigo]])</f>
-        <v/>
-      </c>
+      <c r="K39" s="16" t="n"/>
       <c r="L39" s="30" t="inlineStr">
         <is>
           <t>ch-37</t>
         </is>
       </c>
-      <c r="M39" s="16">
-        <f>SUMIFS(Tabla3[EXISTENCIA ACTUAL],Tabla3[CODIGO UNITARIO],Tabla3[[#This Row], [CODIGO UNITARIO]])</f>
-        <v/>
-      </c>
+      <c r="M39" s="16" t="n"/>
     </row>
     <row r="40" ht="18.75" customHeight="1">
       <c r="A40" s="18" t="inlineStr">
@@ -3648,28 +3196,16 @@
         </is>
       </c>
       <c r="G40" s="28" t="n"/>
-      <c r="H40" s="28">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,"Agotado",          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],"Menor al Mìnimo",    "Ok") )</f>
-        <v/>
-      </c>
-      <c r="I40" s="29">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,0,          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],1,    2) )</f>
-        <v/>
-      </c>
+      <c r="H40" s="28" t="n"/>
+      <c r="I40" s="29" t="n"/>
       <c r="J40" s="28" t="n"/>
-      <c r="K40" s="16">
-        <f>SUMIFS(Tabla5[cantidad],Tabla5[Codigo],Tabla3[[#This Row], [Codigo]])</f>
-        <v/>
-      </c>
+      <c r="K40" s="16" t="n"/>
       <c r="L40" s="18" t="inlineStr">
         <is>
           <t>E356-15-290</t>
         </is>
       </c>
-      <c r="M40" s="16">
-        <f>SUMIFS(Tabla3[EXISTENCIA ACTUAL],Tabla3[CODIGO UNITARIO],Tabla3[[#This Row], [CODIGO UNITARIO]])</f>
-        <v/>
-      </c>
+      <c r="M40" s="16" t="n"/>
     </row>
     <row r="41" ht="18.75" customHeight="1">
       <c r="A41" s="16" t="n">
@@ -3701,28 +3237,16 @@
           <t>2A-1</t>
         </is>
       </c>
-      <c r="H41" s="28">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,"Agotado",          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],"Menor al Mìnimo",    "Ok") )</f>
-        <v/>
-      </c>
-      <c r="I41" s="29">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,0,          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],1,    2) )</f>
-        <v/>
-      </c>
+      <c r="H41" s="28" t="n"/>
+      <c r="I41" s="29" t="n"/>
       <c r="J41" s="28" t="n"/>
-      <c r="K41" s="16">
-        <f>SUMIFS(Tabla5[cantidad],Tabla5[Codigo],Tabla3[[#This Row], [Codigo]])</f>
-        <v/>
-      </c>
+      <c r="K41" s="16" t="n"/>
       <c r="L41" s="32" t="inlineStr">
         <is>
           <t>93229708</t>
         </is>
       </c>
-      <c r="M41" s="16">
-        <f>SUMIFS(Tabla3[EXISTENCIA ACTUAL],Tabla3[CODIGO UNITARIO],Tabla3[[#This Row], [CODIGO UNITARIO]])</f>
-        <v/>
-      </c>
+      <c r="M41" s="16" t="n"/>
     </row>
     <row r="42" ht="18.75" customHeight="1">
       <c r="A42" s="16" t="n">
@@ -3746,28 +3270,16 @@
         </is>
       </c>
       <c r="G42" s="28" t="n"/>
-      <c r="H42" s="28">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,"Agotado",          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],"Menor al Mìnimo",    "Ok") )</f>
-        <v/>
-      </c>
-      <c r="I42" s="31">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,0,          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],1,    2) )</f>
-        <v/>
-      </c>
+      <c r="H42" s="28" t="n"/>
+      <c r="I42" s="31" t="n"/>
       <c r="J42" s="28" t="n"/>
-      <c r="K42" s="16">
-        <f>SUMIFS(Tabla5[cantidad],Tabla5[Codigo],Tabla3[[#This Row], [Codigo]])</f>
-        <v/>
-      </c>
+      <c r="K42" s="16" t="n"/>
       <c r="L42" s="32" t="inlineStr">
         <is>
           <t>11735</t>
         </is>
       </c>
-      <c r="M42" s="16">
-        <f>SUMIFS(Tabla3[EXISTENCIA ACTUAL],Tabla3[CODIGO UNITARIO],Tabla3[[#This Row], [CODIGO UNITARIO]])</f>
-        <v/>
-      </c>
+      <c r="M42" s="16" t="n"/>
     </row>
     <row r="43" ht="18.75" customHeight="1">
       <c r="A43" s="18" t="inlineStr">
@@ -3793,26 +3305,14 @@
         </is>
       </c>
       <c r="G43" s="28" t="n"/>
-      <c r="H43" s="28">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,"Agotado",          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],"Menor al Mìnimo",    "Ok") )</f>
-        <v/>
-      </c>
-      <c r="I43" s="29">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,0,          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],1,    2) )</f>
-        <v/>
-      </c>
+      <c r="H43" s="28" t="n"/>
+      <c r="I43" s="29" t="n"/>
       <c r="J43" s="28" t="n"/>
-      <c r="K43" s="16">
-        <f>SUMIFS(Tabla5[cantidad],Tabla5[Codigo],Tabla3[[#This Row], [Codigo]])</f>
-        <v/>
-      </c>
+      <c r="K43" s="16" t="n"/>
       <c r="L43" s="16" t="n">
         <v>770101229</v>
       </c>
-      <c r="M43" s="16">
-        <f>SUMIFS(Tabla3[EXISTENCIA ACTUAL],Tabla3[CODIGO UNITARIO],Tabla3[[#This Row], [CODIGO UNITARIO]])</f>
-        <v/>
-      </c>
+      <c r="M43" s="16" t="n"/>
     </row>
     <row r="44" ht="18.75" customHeight="1">
       <c r="A44" s="18" t="inlineStr">
@@ -3842,28 +3342,16 @@
         </is>
       </c>
       <c r="G44" s="28" t="n"/>
-      <c r="H44" s="28">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,"Agotado",          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],"Menor al Mìnimo",    "Ok") )</f>
-        <v/>
-      </c>
-      <c r="I44" s="31">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,0,          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],1,    2) )</f>
-        <v/>
-      </c>
+      <c r="H44" s="28" t="n"/>
+      <c r="I44" s="31" t="n"/>
       <c r="J44" s="28" t="n"/>
-      <c r="K44" s="16">
-        <f>SUMIFS(Tabla5[cantidad],Tabla5[Codigo],Tabla3[[#This Row], [Codigo]])</f>
-        <v/>
-      </c>
+      <c r="K44" s="16" t="n"/>
       <c r="L44" s="18" t="inlineStr">
         <is>
           <t>Ee501-15-290</t>
         </is>
       </c>
-      <c r="M44" s="16">
-        <f>SUMIFS(Tabla3[EXISTENCIA ACTUAL],Tabla3[CODIGO UNITARIO],Tabla3[[#This Row], [CODIGO UNITARIO]])</f>
-        <v/>
-      </c>
+      <c r="M44" s="16" t="n"/>
     </row>
     <row r="45" ht="18.75" customHeight="1">
       <c r="A45" s="18" t="inlineStr">
@@ -3897,28 +3385,16 @@
           <t>1A-5</t>
         </is>
       </c>
-      <c r="H45" s="28">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,"Agotado",          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],"Menor al Mìnimo",    "Ok") )</f>
-        <v/>
-      </c>
-      <c r="I45" s="29">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,0,          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],1,    2) )</f>
-        <v/>
-      </c>
+      <c r="H45" s="28" t="n"/>
+      <c r="I45" s="29" t="n"/>
       <c r="J45" s="28" t="n"/>
-      <c r="K45" s="16">
-        <f>SUMIFS(Tabla5[cantidad],Tabla5[Codigo],Tabla3[[#This Row], [Codigo]])</f>
-        <v/>
-      </c>
+      <c r="K45" s="16" t="n"/>
       <c r="L45" s="18" t="inlineStr">
         <is>
           <t>KRE-3102</t>
         </is>
       </c>
-      <c r="M45" s="16">
-        <f>SUMIFS(Tabla3[EXISTENCIA ACTUAL],Tabla3[CODIGO UNITARIO],Tabla3[[#This Row], [CODIGO UNITARIO]])</f>
-        <v/>
-      </c>
+      <c r="M45" s="16" t="n"/>
     </row>
     <row r="46" ht="18.75" customHeight="1">
       <c r="A46" s="18" t="inlineStr">
@@ -3948,28 +3424,16 @@
         </is>
       </c>
       <c r="G46" s="28" t="n"/>
-      <c r="H46" s="28">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,"Agotado",          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],"Menor al Mìnimo",    "Ok") )</f>
-        <v/>
-      </c>
-      <c r="I46" s="29">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,0,          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],1,    2) )</f>
-        <v/>
-      </c>
+      <c r="H46" s="28" t="n"/>
+      <c r="I46" s="29" t="n"/>
       <c r="J46" s="28" t="n"/>
-      <c r="K46" s="16">
-        <f>SUMIFS(Tabla5[cantidad],Tabla5[Codigo],Tabla3[[#This Row], [Codigo]])</f>
-        <v/>
-      </c>
+      <c r="K46" s="16" t="n"/>
       <c r="L46" s="18" t="inlineStr">
         <is>
           <t>B61K-15-290B</t>
         </is>
       </c>
-      <c r="M46" s="16">
-        <f>SUMIFS(Tabla3[EXISTENCIA ACTUAL],Tabla3[CODIGO UNITARIO],Tabla3[[#This Row], [CODIGO UNITARIO]])</f>
-        <v/>
-      </c>
+      <c r="M46" s="16" t="n"/>
     </row>
     <row r="47" ht="18.75" customHeight="1">
       <c r="A47" s="18" t="inlineStr">
@@ -4003,28 +3467,16 @@
           <t>1A-9</t>
         </is>
       </c>
-      <c r="H47" s="28">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,"Agotado",          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],"Menor al Mìnimo",    "Ok") )</f>
-        <v/>
-      </c>
-      <c r="I47" s="31">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,0,          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],1,    2) )</f>
-        <v/>
-      </c>
+      <c r="H47" s="28" t="n"/>
+      <c r="I47" s="31" t="n"/>
       <c r="J47" s="28" t="n"/>
-      <c r="K47" s="16">
-        <f>SUMIFS(Tabla5[cantidad],Tabla5[Codigo],Tabla3[[#This Row], [Codigo]])</f>
-        <v/>
-      </c>
+      <c r="K47" s="16" t="n"/>
       <c r="L47" s="30" t="inlineStr">
         <is>
           <t>kre-3106</t>
         </is>
       </c>
-      <c r="M47" s="16">
-        <f>SUMIFS(Tabla3[EXISTENCIA ACTUAL],Tabla3[CODIGO UNITARIO],Tabla3[[#This Row], [CODIGO UNITARIO]])</f>
-        <v/>
-      </c>
+      <c r="M47" s="16" t="n"/>
     </row>
     <row r="48" ht="18.75" customHeight="1">
       <c r="A48" s="18" t="inlineStr">
@@ -4048,28 +3500,16 @@
         </is>
       </c>
       <c r="G48" s="28" t="n"/>
-      <c r="H48" s="28">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,"Agotado",          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],"Menor al Mìnimo",    "Ok") )</f>
-        <v/>
-      </c>
-      <c r="I48" s="29">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,0,          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],1,    2) )</f>
-        <v/>
-      </c>
+      <c r="H48" s="28" t="n"/>
+      <c r="I48" s="29" t="n"/>
       <c r="J48" s="28" t="n"/>
-      <c r="K48" s="16">
-        <f>SUMIFS(Tabla5[cantidad],Tabla5[Codigo],Tabla3[[#This Row], [Codigo]])</f>
-        <v/>
-      </c>
+      <c r="K48" s="16" t="n"/>
       <c r="L48" s="30" t="inlineStr">
         <is>
           <t>ch-37</t>
         </is>
       </c>
-      <c r="M48" s="16">
-        <f>SUMIFS(Tabla3[EXISTENCIA ACTUAL],Tabla3[CODIGO UNITARIO],Tabla3[[#This Row], [CODIGO UNITARIO]])</f>
-        <v/>
-      </c>
+      <c r="M48" s="16" t="n"/>
     </row>
     <row r="49" ht="18.75" customHeight="1">
       <c r="A49" s="16" t="n">
@@ -4101,28 +3541,16 @@
           <t>1A-8</t>
         </is>
       </c>
-      <c r="H49" s="28">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,"Agotado",          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],"Menor al Mìnimo",    "Ok") )</f>
-        <v/>
-      </c>
-      <c r="I49" s="29">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,0,          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],1,    2) )</f>
-        <v/>
-      </c>
+      <c r="H49" s="28" t="n"/>
+      <c r="I49" s="29" t="n"/>
       <c r="J49" s="28" t="n"/>
-      <c r="K49" s="16">
-        <f>SUMIFS(Tabla5[cantidad],Tabla5[Codigo],Tabla3[[#This Row], [Codigo]])</f>
-        <v/>
-      </c>
+      <c r="K49" s="16" t="n"/>
       <c r="L49" s="30" t="inlineStr">
         <is>
           <t>kre-3102</t>
         </is>
       </c>
-      <c r="M49" s="16">
-        <f>SUMIFS(Tabla3[EXISTENCIA ACTUAL],Tabla3[CODIGO UNITARIO],Tabla3[[#This Row], [CODIGO UNITARIO]])</f>
-        <v/>
-      </c>
+      <c r="M49" s="16" t="n"/>
     </row>
     <row r="50" ht="18.75" customHeight="1">
       <c r="A50" s="18" t="inlineStr">
@@ -4148,28 +3576,16 @@
         </is>
       </c>
       <c r="G50" s="28" t="n"/>
-      <c r="H50" s="28">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,"Agotado",          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],"Menor al Mìnimo",    "Ok") )</f>
-        <v/>
-      </c>
-      <c r="I50" s="31">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,0,          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],1,    2) )</f>
-        <v/>
-      </c>
+      <c r="H50" s="28" t="n"/>
+      <c r="I50" s="31" t="n"/>
       <c r="J50" s="28" t="n"/>
-      <c r="K50" s="16">
-        <f>SUMIFS(Tabla5[cantidad],Tabla5[Codigo],Tabla3[[#This Row], [Codigo]])</f>
-        <v/>
-      </c>
+      <c r="K50" s="16" t="n"/>
       <c r="L50" s="30" t="inlineStr">
         <is>
           <t>ch-66</t>
         </is>
       </c>
-      <c r="M50" s="16">
-        <f>SUMIFS(Tabla3[EXISTENCIA ACTUAL],Tabla3[CODIGO UNITARIO],Tabla3[[#This Row], [CODIGO UNITARIO]])</f>
-        <v/>
-      </c>
+      <c r="M50" s="16" t="n"/>
     </row>
     <row r="51" ht="18.75" customHeight="1">
       <c r="A51" s="16" t="n">
@@ -4201,26 +3617,14 @@
           <t>7e-z1</t>
         </is>
       </c>
-      <c r="H51" s="28">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,"Agotado",          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],"Menor al Mìnimo",    "Ok") )</f>
-        <v/>
-      </c>
-      <c r="I51" s="31">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,0,          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],1,    2) )</f>
-        <v/>
-      </c>
+      <c r="H51" s="28" t="n"/>
+      <c r="I51" s="31" t="n"/>
       <c r="J51" s="28" t="n"/>
-      <c r="K51" s="16">
-        <f>SUMIFS(Tabla5[cantidad],Tabla5[Codigo],Tabla3[[#This Row], [Codigo]])</f>
-        <v/>
-      </c>
+      <c r="K51" s="16" t="n"/>
       <c r="L51" s="16" t="n">
         <v>25632</v>
       </c>
-      <c r="M51" s="16">
-        <f>SUMIFS(Tabla3[EXISTENCIA ACTUAL],Tabla3[CODIGO UNITARIO],Tabla3[[#This Row], [CODIGO UNITARIO]])</f>
-        <v/>
-      </c>
+      <c r="M51" s="16" t="n"/>
     </row>
     <row r="52" ht="18.75" customHeight="1">
       <c r="A52" s="18" t="inlineStr">
@@ -4254,28 +3658,16 @@
           <t>7E-Z1</t>
         </is>
       </c>
-      <c r="H52" s="28">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,"Agotado",          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],"Menor al Mìnimo",    "Ok") )</f>
-        <v/>
-      </c>
-      <c r="I52" s="31">
-        <f>IF(Tabla3[[#This Row], [EXISTENCIA ACTUAL]]=0,0,          IF(  Tabla3[[#This Row], [EXISTENCIA ACTUAL]]&lt;Tabla3[[#This Row], [STOCK MÍNIMO]],1,    2) )</f>
-        <v/>
-      </c>
+      <c r="H52" s="28" t="n"/>
+      <c r="I52" s="31" t="n"/>
       <c r="J52" s="28" t="n"/>
-      <c r="K52" s="16">
-        <f>SUMIFS(Tabla5[cantidad],Tabla5[Codigo],Tabla3[[#This Row], [Codigo]])</f>
-        <v/>
-      </c>
+      <c r="K52" s="16" t="n"/>
       <c r="L52" s="30" t="inlineStr">
         <is>
           <t>ch-78</t>
         </is>
       </c>
-      <c r="M52" s="16">
-        <f>SUMIFS(Tabla3[EXISTENCIA ACTUAL],Tabla3[CODIGO UNITARIO],Tabla3[[#This Row], [CODIGO UNITARIO]])</f>
-        <v/>
-      </c>
+      <c r="M52" s="16" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4443,17 +3835,17 @@
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1">
-      <c r="A2" s="11" t="n">
-        <v>45184</v>
-      </c>
-      <c r="B2" s="18" t="inlineStr">
-        <is>
-          <t>ch-38</t>
-        </is>
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>dft</t>
+        </is>
+      </c>
+      <c r="B2" s="18" t="n">
+        <v>166</v>
       </c>
       <c r="C2" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">tubo paso agua corsa^ </t>
+          <t>323</t>
         </is>
       </c>
       <c r="D2" s="13" t="n">
@@ -4474,10 +3866,7 @@
           <t>ch-38</t>
         </is>
       </c>
-      <c r="H2" s="15">
-        <f>TEXT(Tabla5[[#This Row], [Fecha]],"MMMM") &amp; TEXT(Tabla5[[#This Row], [Fecha]],"yy")</f>
-        <v/>
-      </c>
+      <c r="H2" s="15" t="n"/>
       <c r="I2" s="16" t="n">
         <v>3</v>
       </c>
@@ -4486,38 +3875,14 @@
       <c r="L2" s="28" t="n"/>
       <c r="M2" s="28" t="n"/>
       <c r="N2" s="16" t="n"/>
-      <c r="O2" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="P2" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="Q2" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="R2" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="S2" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&lt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="T2" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&gt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="U2" s="16">
-        <f>IFERROR(Tabla5[[#This Row], [CANT VENDIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
-      <c r="V2" s="13">
-        <f>IFERROR(Tabla5[[#This Row], [CANT ADQUIRIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
+      <c r="O2" s="16" t="n"/>
+      <c r="P2" s="16" t="n"/>
+      <c r="Q2" s="16" t="n"/>
+      <c r="R2" s="16" t="n"/>
+      <c r="S2" s="16" t="n"/>
+      <c r="T2" s="16" t="n"/>
+      <c r="U2" s="16" t="n"/>
+      <c r="V2" s="13" t="n"/>
       <c r="W2" s="13" t="n">
         <v>9800</v>
       </c>
@@ -4555,10 +3920,7 @@
       <c r="G3" s="13" t="n">
         <v>7700273904</v>
       </c>
-      <c r="H3" s="15">
-        <f>TEXT(Tabla5[[#This Row], [Fecha]],"MMMM") &amp; TEXT(Tabla5[[#This Row], [Fecha]],"yy")</f>
-        <v/>
-      </c>
+      <c r="H3" s="15" t="n"/>
       <c r="I3" s="16" t="n">
         <v>1</v>
       </c>
@@ -4567,38 +3929,14 @@
       <c r="L3" s="28" t="n"/>
       <c r="M3" s="28" t="n"/>
       <c r="N3" s="16" t="n"/>
-      <c r="O3" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="P3" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="Q3" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="R3" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="S3" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&lt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="T3" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&gt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="U3" s="16">
-        <f>IFERROR(Tabla5[[#This Row], [CANT VENDIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
-      <c r="V3" s="13">
-        <f>IFERROR(Tabla5[[#This Row], [CANT ADQUIRIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
+      <c r="O3" s="16" t="n"/>
+      <c r="P3" s="16" t="n"/>
+      <c r="Q3" s="16" t="n"/>
+      <c r="R3" s="16" t="n"/>
+      <c r="S3" s="16" t="n"/>
+      <c r="T3" s="16" t="n"/>
+      <c r="U3" s="16" t="n"/>
+      <c r="V3" s="13" t="n"/>
       <c r="W3" s="13" t="n">
         <v>8620</v>
       </c>
@@ -4640,10 +3978,7 @@
           <t>valv</t>
         </is>
       </c>
-      <c r="H4" s="15">
-        <f>TEXT(Tabla5[[#This Row], [Fecha]],"MMMM") &amp; TEXT(Tabla5[[#This Row], [Fecha]],"yy")</f>
-        <v/>
-      </c>
+      <c r="H4" s="15" t="n"/>
       <c r="I4" s="16" t="n">
         <v>31</v>
       </c>
@@ -4652,38 +3987,14 @@
       <c r="L4" s="28" t="n"/>
       <c r="M4" s="28" t="n"/>
       <c r="N4" s="16" t="n"/>
-      <c r="O4" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="P4" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="Q4" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="R4" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="S4" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&lt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="T4" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&gt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="U4" s="16">
-        <f>IFERROR(Tabla5[[#This Row], [CANT VENDIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
-      <c r="V4" s="13">
-        <f>IFERROR(Tabla5[[#This Row], [CANT ADQUIRIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
+      <c r="O4" s="16" t="n"/>
+      <c r="P4" s="16" t="n"/>
+      <c r="Q4" s="16" t="n"/>
+      <c r="R4" s="16" t="n"/>
+      <c r="S4" s="16" t="n"/>
+      <c r="T4" s="16" t="n"/>
+      <c r="U4" s="16" t="n"/>
+      <c r="V4" s="13" t="n"/>
       <c r="W4" s="13" t="n">
         <v>8083.075</v>
       </c>
@@ -4725,10 +4036,7 @@
           <t>valv</t>
         </is>
       </c>
-      <c r="H5" s="15">
-        <f>TEXT(Tabla5[[#This Row], [Fecha]],"MMMM") &amp; TEXT(Tabla5[[#This Row], [Fecha]],"yy")</f>
-        <v/>
-      </c>
+      <c r="H5" s="15" t="n"/>
       <c r="I5" s="16" t="n">
         <v>22</v>
       </c>
@@ -4737,38 +4045,14 @@
       <c r="L5" s="28" t="n"/>
       <c r="M5" s="28" t="n"/>
       <c r="N5" s="16" t="n"/>
-      <c r="O5" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="P5" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="Q5" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="R5" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="S5" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&lt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="T5" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&gt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="U5" s="16">
-        <f>IFERROR(Tabla5[[#This Row], [CANT VENDIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
-      <c r="V5" s="13">
-        <f>IFERROR(Tabla5[[#This Row], [CANT ADQUIRIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
+      <c r="O5" s="16" t="n"/>
+      <c r="P5" s="16" t="n"/>
+      <c r="Q5" s="16" t="n"/>
+      <c r="R5" s="16" t="n"/>
+      <c r="S5" s="16" t="n"/>
+      <c r="T5" s="16" t="n"/>
+      <c r="U5" s="16" t="n"/>
+      <c r="V5" s="13" t="n"/>
       <c r="W5" s="13" t="n">
         <v>10000</v>
       </c>
@@ -4810,10 +4094,7 @@
           <t>pcvaveo</t>
         </is>
       </c>
-      <c r="H6" s="15">
-        <f>TEXT(Tabla5[[#This Row], [Fecha]],"MMMM") &amp; TEXT(Tabla5[[#This Row], [Fecha]],"yy")</f>
-        <v/>
-      </c>
+      <c r="H6" s="15" t="n"/>
       <c r="I6" s="16" t="n">
         <v>1</v>
       </c>
@@ -4822,38 +4103,14 @@
       <c r="L6" s="28" t="n"/>
       <c r="M6" s="28" t="n"/>
       <c r="N6" s="16" t="n"/>
-      <c r="O6" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="P6" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="Q6" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="R6" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="S6" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&lt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="T6" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&gt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="U6" s="16">
-        <f>IFERROR(Tabla5[[#This Row], [CANT VENDIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
-      <c r="V6" s="13">
-        <f>IFERROR(Tabla5[[#This Row], [CANT ADQUIRIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
+      <c r="O6" s="16" t="n"/>
+      <c r="P6" s="16" t="n"/>
+      <c r="Q6" s="16" t="n"/>
+      <c r="R6" s="16" t="n"/>
+      <c r="S6" s="16" t="n"/>
+      <c r="T6" s="16" t="n"/>
+      <c r="U6" s="16" t="n"/>
+      <c r="V6" s="13" t="n"/>
       <c r="W6" s="13" t="n">
         <v>14686.98</v>
       </c>
@@ -4893,10 +4150,7 @@
       <c r="G7" s="14" t="n">
         <v>18118</v>
       </c>
-      <c r="H7" s="15">
-        <f>TEXT(Tabla5[[#This Row], [Fecha]],"MMMM") &amp; TEXT(Tabla5[[#This Row], [Fecha]],"yy")</f>
-        <v/>
-      </c>
+      <c r="H7" s="15" t="n"/>
       <c r="I7" s="16" t="n">
         <v>3</v>
       </c>
@@ -4905,38 +4159,14 @@
       <c r="L7" s="28" t="n"/>
       <c r="M7" s="28" t="n"/>
       <c r="N7" s="16" t="n"/>
-      <c r="O7" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="P7" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="Q7" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="R7" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="S7" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&lt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="T7" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&gt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="U7" s="16">
-        <f>IFERROR(Tabla5[[#This Row], [CANT VENDIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
-      <c r="V7" s="13">
-        <f>IFERROR(Tabla5[[#This Row], [CANT ADQUIRIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
+      <c r="O7" s="16" t="n"/>
+      <c r="P7" s="16" t="n"/>
+      <c r="Q7" s="16" t="n"/>
+      <c r="R7" s="16" t="n"/>
+      <c r="S7" s="16" t="n"/>
+      <c r="T7" s="16" t="n"/>
+      <c r="U7" s="16" t="n"/>
+      <c r="V7" s="13" t="n"/>
       <c r="W7" s="13" t="n">
         <v>6937.2</v>
       </c>
@@ -4974,10 +4204,7 @@
       <c r="G8" s="14" t="n">
         <v>96991801</v>
       </c>
-      <c r="H8" s="15">
-        <f>TEXT(Tabla5[[#This Row], [Fecha]],"MMMM") &amp; TEXT(Tabla5[[#This Row], [Fecha]],"yy")</f>
-        <v/>
-      </c>
+      <c r="H8" s="15" t="n"/>
       <c r="I8" s="16" t="n">
         <v>2</v>
       </c>
@@ -4986,38 +4213,14 @@
       <c r="L8" s="28" t="n"/>
       <c r="M8" s="28" t="n"/>
       <c r="N8" s="16" t="n"/>
-      <c r="O8" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="P8" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="Q8" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="R8" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="S8" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&lt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="T8" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&gt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="U8" s="16">
-        <f>IFERROR(Tabla5[[#This Row], [CANT VENDIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
-      <c r="V8" s="13">
-        <f>IFERROR(Tabla5[[#This Row], [CANT ADQUIRIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
+      <c r="O8" s="16" t="n"/>
+      <c r="P8" s="16" t="n"/>
+      <c r="Q8" s="16" t="n"/>
+      <c r="R8" s="16" t="n"/>
+      <c r="S8" s="16" t="n"/>
+      <c r="T8" s="16" t="n"/>
+      <c r="U8" s="16" t="n"/>
+      <c r="V8" s="13" t="n"/>
       <c r="W8" s="13" t="n">
         <v>17035.2</v>
       </c>
@@ -5055,10 +4258,7 @@
       <c r="G9" s="14" t="n">
         <v>18118</v>
       </c>
-      <c r="H9" s="15">
-        <f>TEXT(Tabla5[[#This Row], [Fecha]],"MMMM") &amp; TEXT(Tabla5[[#This Row], [Fecha]],"yy")</f>
-        <v/>
-      </c>
+      <c r="H9" s="15" t="n"/>
       <c r="I9" s="16" t="n">
         <v>4</v>
       </c>
@@ -5067,38 +4267,14 @@
       <c r="L9" s="28" t="n"/>
       <c r="M9" s="28" t="n"/>
       <c r="N9" s="16" t="n"/>
-      <c r="O9" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="P9" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="Q9" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="R9" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="S9" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&lt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="T9" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&gt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="U9" s="16">
-        <f>IFERROR(Tabla5[[#This Row], [CANT VENDIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
-      <c r="V9" s="13">
-        <f>IFERROR(Tabla5[[#This Row], [CANT ADQUIRIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
+      <c r="O9" s="16" t="n"/>
+      <c r="P9" s="16" t="n"/>
+      <c r="Q9" s="16" t="n"/>
+      <c r="R9" s="16" t="n"/>
+      <c r="S9" s="16" t="n"/>
+      <c r="T9" s="16" t="n"/>
+      <c r="U9" s="16" t="n"/>
+      <c r="V9" s="13" t="n"/>
       <c r="W9" s="13" t="n">
         <v>8167.445999999999</v>
       </c>
@@ -5138,10 +4314,7 @@
       <c r="G10" s="13" t="n">
         <v>14320</v>
       </c>
-      <c r="H10" s="15">
-        <f>TEXT(Tabla5[[#This Row], [Fecha]],"MMMM") &amp; TEXT(Tabla5[[#This Row], [Fecha]],"yy")</f>
-        <v/>
-      </c>
+      <c r="H10" s="15" t="n"/>
       <c r="I10" s="16" t="n">
         <v>1</v>
       </c>
@@ -5150,38 +4323,14 @@
       <c r="L10" s="28" t="n"/>
       <c r="M10" s="28" t="n"/>
       <c r="N10" s="16" t="n"/>
-      <c r="O10" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="P10" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="Q10" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="R10" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="S10" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&lt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="T10" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&gt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="U10" s="16">
-        <f>IFERROR(Tabla5[[#This Row], [CANT VENDIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
-      <c r="V10" s="13">
-        <f>IFERROR(Tabla5[[#This Row], [CANT ADQUIRIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
+      <c r="O10" s="16" t="n"/>
+      <c r="P10" s="16" t="n"/>
+      <c r="Q10" s="16" t="n"/>
+      <c r="R10" s="16" t="n"/>
+      <c r="S10" s="16" t="n"/>
+      <c r="T10" s="16" t="n"/>
+      <c r="U10" s="16" t="n"/>
+      <c r="V10" s="13" t="n"/>
       <c r="W10" s="13" t="n">
         <v>6937.2</v>
       </c>
@@ -5219,10 +4368,7 @@
       <c r="G11" s="13" t="n">
         <v>24516476</v>
       </c>
-      <c r="H11" s="15">
-        <f>TEXT(Tabla5[[#This Row], [Fecha]],"MMMM") &amp; TEXT(Tabla5[[#This Row], [Fecha]],"yy")</f>
-        <v/>
-      </c>
+      <c r="H11" s="15" t="n"/>
       <c r="I11" s="16" t="n">
         <v>4</v>
       </c>
@@ -5231,38 +4377,14 @@
       <c r="L11" s="28" t="n"/>
       <c r="M11" s="28" t="n"/>
       <c r="N11" s="16" t="n"/>
-      <c r="O11" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="P11" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="Q11" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="R11" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="S11" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&lt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="T11" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&gt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="U11" s="16">
-        <f>IFERROR(Tabla5[[#This Row], [CANT VENDIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
-      <c r="V11" s="13">
-        <f>IFERROR(Tabla5[[#This Row], [CANT ADQUIRIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
+      <c r="O11" s="16" t="n"/>
+      <c r="P11" s="16" t="n"/>
+      <c r="Q11" s="16" t="n"/>
+      <c r="R11" s="16" t="n"/>
+      <c r="S11" s="16" t="n"/>
+      <c r="T11" s="16" t="n"/>
+      <c r="U11" s="16" t="n"/>
+      <c r="V11" s="13" t="n"/>
       <c r="W11" s="13" t="n">
         <v>6729.45</v>
       </c>
@@ -5300,10 +4422,7 @@
       <c r="G12" s="13" t="n">
         <v>96535300</v>
       </c>
-      <c r="H12" s="15">
-        <f>TEXT(Tabla5[[#This Row], [Fecha]],"MMMM") &amp; TEXT(Tabla5[[#This Row], [Fecha]],"yy")</f>
-        <v/>
-      </c>
+      <c r="H12" s="15" t="n"/>
       <c r="I12" s="16" t="n">
         <v>1</v>
       </c>
@@ -5312,38 +4431,14 @@
       <c r="L12" s="28" t="n"/>
       <c r="M12" s="28" t="n"/>
       <c r="N12" s="16" t="n"/>
-      <c r="O12" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="P12" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="Q12" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="R12" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="S12" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&lt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="T12" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&gt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="U12" s="16">
-        <f>IFERROR(Tabla5[[#This Row], [CANT VENDIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
-      <c r="V12" s="13">
-        <f>IFERROR(Tabla5[[#This Row], [CANT ADQUIRIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
+      <c r="O12" s="16" t="n"/>
+      <c r="P12" s="16" t="n"/>
+      <c r="Q12" s="16" t="n"/>
+      <c r="R12" s="16" t="n"/>
+      <c r="S12" s="16" t="n"/>
+      <c r="T12" s="16" t="n"/>
+      <c r="U12" s="16" t="n"/>
+      <c r="V12" s="13" t="n"/>
       <c r="W12" s="13" t="n">
         <v>21800</v>
       </c>
@@ -5383,10 +4478,7 @@
       <c r="G13" s="14" t="n">
         <v>18118</v>
       </c>
-      <c r="H13" s="15">
-        <f>TEXT(Tabla5[[#This Row], [Fecha]],"MMMM") &amp; TEXT(Tabla5[[#This Row], [Fecha]],"yy")</f>
-        <v/>
-      </c>
+      <c r="H13" s="15" t="n"/>
       <c r="I13" s="16" t="n">
         <v>4</v>
       </c>
@@ -5395,38 +4487,14 @@
       <c r="L13" s="28" t="n"/>
       <c r="M13" s="28" t="n"/>
       <c r="N13" s="16" t="n"/>
-      <c r="O13" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="P13" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="Q13" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="R13" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="S13" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&lt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="T13" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&gt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="U13" s="16">
-        <f>IFERROR(Tabla5[[#This Row], [CANT VENDIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
-      <c r="V13" s="13">
-        <f>IFERROR(Tabla5[[#This Row], [CANT ADQUIRIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
+      <c r="O13" s="16" t="n"/>
+      <c r="P13" s="16" t="n"/>
+      <c r="Q13" s="16" t="n"/>
+      <c r="R13" s="16" t="n"/>
+      <c r="S13" s="16" t="n"/>
+      <c r="T13" s="16" t="n"/>
+      <c r="U13" s="16" t="n"/>
+      <c r="V13" s="13" t="n"/>
       <c r="W13" s="13" t="n">
         <v>0</v>
       </c>
@@ -5464,10 +4532,7 @@
       <c r="G14" s="13" t="n">
         <v>14320</v>
       </c>
-      <c r="H14" s="15">
-        <f>TEXT(Tabla5[[#This Row], [Fecha]],"MMMM") &amp; TEXT(Tabla5[[#This Row], [Fecha]],"yy")</f>
-        <v/>
-      </c>
+      <c r="H14" s="15" t="n"/>
       <c r="I14" s="16" t="n">
         <v>3</v>
       </c>
@@ -5476,38 +4541,14 @@
       <c r="L14" s="28" t="n"/>
       <c r="M14" s="28" t="n"/>
       <c r="N14" s="16" t="n"/>
-      <c r="O14" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="P14" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="Q14" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="R14" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="S14" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&lt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="T14" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&gt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="U14" s="16">
-        <f>IFERROR(Tabla5[[#This Row], [CANT VENDIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
-      <c r="V14" s="13">
-        <f>IFERROR(Tabla5[[#This Row], [CANT ADQUIRIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
+      <c r="O14" s="16" t="n"/>
+      <c r="P14" s="16" t="n"/>
+      <c r="Q14" s="16" t="n"/>
+      <c r="R14" s="16" t="n"/>
+      <c r="S14" s="16" t="n"/>
+      <c r="T14" s="16" t="n"/>
+      <c r="U14" s="16" t="n"/>
+      <c r="V14" s="13" t="n"/>
       <c r="W14" s="13" t="n">
         <v>9508.1</v>
       </c>
@@ -5549,10 +4590,7 @@
           <t>pcvaveo</t>
         </is>
       </c>
-      <c r="H15" s="15">
-        <f>TEXT(Tabla5[[#This Row], [Fecha]],"MMMM") &amp; TEXT(Tabla5[[#This Row], [Fecha]],"yy")</f>
-        <v/>
-      </c>
+      <c r="H15" s="15" t="n"/>
       <c r="I15" s="16" t="n">
         <v>3</v>
       </c>
@@ -5561,38 +4599,14 @@
       <c r="L15" s="28" t="n"/>
       <c r="M15" s="28" t="n"/>
       <c r="N15" s="16" t="n"/>
-      <c r="O15" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="P15" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="Q15" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="R15" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="S15" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&lt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="T15" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&gt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="U15" s="16">
-        <f>IFERROR(Tabla5[[#This Row], [CANT VENDIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
-      <c r="V15" s="13">
-        <f>IFERROR(Tabla5[[#This Row], [CANT ADQUIRIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
+      <c r="O15" s="16" t="n"/>
+      <c r="P15" s="16" t="n"/>
+      <c r="Q15" s="16" t="n"/>
+      <c r="R15" s="16" t="n"/>
+      <c r="S15" s="16" t="n"/>
+      <c r="T15" s="16" t="n"/>
+      <c r="U15" s="16" t="n"/>
+      <c r="V15" s="13" t="n"/>
       <c r="W15" s="13" t="n">
         <v>20391.84</v>
       </c>
@@ -5632,10 +4646,7 @@
           <t>pcvaveo</t>
         </is>
       </c>
-      <c r="H16" s="15">
-        <f>TEXT(Tabla5[[#This Row], [Fecha]],"MMMM") &amp; TEXT(Tabla5[[#This Row], [Fecha]],"yy")</f>
-        <v/>
-      </c>
+      <c r="H16" s="15" t="n"/>
       <c r="I16" s="16" t="n">
         <v>2</v>
       </c>
@@ -5644,38 +4655,14 @@
       <c r="L16" s="28" t="n"/>
       <c r="M16" s="28" t="n"/>
       <c r="N16" s="16" t="n"/>
-      <c r="O16" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="P16" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="Q16" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="R16" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="S16" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&lt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="T16" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&gt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="U16" s="16">
-        <f>IFERROR(Tabla5[[#This Row], [CANT VENDIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
-      <c r="V16" s="13">
-        <f>IFERROR(Tabla5[[#This Row], [CANT ADQUIRIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
+      <c r="O16" s="16" t="n"/>
+      <c r="P16" s="16" t="n"/>
+      <c r="Q16" s="16" t="n"/>
+      <c r="R16" s="16" t="n"/>
+      <c r="S16" s="16" t="n"/>
+      <c r="T16" s="16" t="n"/>
+      <c r="U16" s="16" t="n"/>
+      <c r="V16" s="13" t="n"/>
       <c r="W16" s="13" t="n">
         <v>0</v>
       </c>
@@ -5711,10 +4698,7 @@
       <c r="G17" s="13" t="n">
         <v>94580183</v>
       </c>
-      <c r="H17" s="15">
-        <f>TEXT(Tabla5[[#This Row], [Fecha]],"MMMM") &amp; TEXT(Tabla5[[#This Row], [Fecha]],"yy")</f>
-        <v/>
-      </c>
+      <c r="H17" s="15" t="n"/>
       <c r="I17" s="16" t="n">
         <v>1</v>
       </c>
@@ -5723,38 +4707,14 @@
       <c r="L17" s="28" t="n"/>
       <c r="M17" s="28" t="n"/>
       <c r="N17" s="16" t="n"/>
-      <c r="O17" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="P17" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="Q17" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="R17" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="S17" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&lt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="T17" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&gt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="U17" s="16">
-        <f>IFERROR(Tabla5[[#This Row], [CANT VENDIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
-      <c r="V17" s="13">
-        <f>IFERROR(Tabla5[[#This Row], [CANT ADQUIRIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
+      <c r="O17" s="16" t="n"/>
+      <c r="P17" s="16" t="n"/>
+      <c r="Q17" s="16" t="n"/>
+      <c r="R17" s="16" t="n"/>
+      <c r="S17" s="16" t="n"/>
+      <c r="T17" s="16" t="n"/>
+      <c r="U17" s="16" t="n"/>
+      <c r="V17" s="13" t="n"/>
       <c r="W17" s="13" t="n">
         <v>0</v>
       </c>
@@ -5794,10 +4754,7 @@
           <t>257-010</t>
         </is>
       </c>
-      <c r="H18" s="15">
-        <f>TEXT(Tabla5[[#This Row], [Fecha]],"MMMM") &amp; TEXT(Tabla5[[#This Row], [Fecha]],"yy")</f>
-        <v/>
-      </c>
+      <c r="H18" s="15" t="n"/>
       <c r="I18" s="16" t="n">
         <v>1</v>
       </c>
@@ -5806,38 +4763,14 @@
       <c r="L18" s="28" t="n"/>
       <c r="M18" s="28" t="n"/>
       <c r="N18" s="16" t="n"/>
-      <c r="O18" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="P18" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="Q18" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="R18" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="S18" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&lt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="T18" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&gt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="U18" s="16">
-        <f>IFERROR(Tabla5[[#This Row], [CANT VENDIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
-      <c r="V18" s="13">
-        <f>IFERROR(Tabla5[[#This Row], [CANT ADQUIRIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
+      <c r="O18" s="16" t="n"/>
+      <c r="P18" s="16" t="n"/>
+      <c r="Q18" s="16" t="n"/>
+      <c r="R18" s="16" t="n"/>
+      <c r="S18" s="16" t="n"/>
+      <c r="T18" s="16" t="n"/>
+      <c r="U18" s="16" t="n"/>
+      <c r="V18" s="13" t="n"/>
       <c r="W18" s="13" t="n">
         <v>29000</v>
       </c>
@@ -5879,10 +4812,7 @@
           <t>257-010</t>
         </is>
       </c>
-      <c r="H19" s="15">
-        <f>TEXT(Tabla5[[#This Row], [Fecha]],"MMMM") &amp; TEXT(Tabla5[[#This Row], [Fecha]],"yy")</f>
-        <v/>
-      </c>
+      <c r="H19" s="15" t="n"/>
       <c r="I19" s="16" t="n">
         <v>1</v>
       </c>
@@ -5891,38 +4821,14 @@
       <c r="L19" s="28" t="n"/>
       <c r="M19" s="28" t="n"/>
       <c r="N19" s="16" t="n"/>
-      <c r="O19" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="P19" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="Q19" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="R19" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="S19" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&lt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="T19" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&gt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="U19" s="16">
-        <f>IFERROR(Tabla5[[#This Row], [CANT VENDIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
-      <c r="V19" s="13">
-        <f>IFERROR(Tabla5[[#This Row], [CANT ADQUIRIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
+      <c r="O19" s="16" t="n"/>
+      <c r="P19" s="16" t="n"/>
+      <c r="Q19" s="16" t="n"/>
+      <c r="R19" s="16" t="n"/>
+      <c r="S19" s="16" t="n"/>
+      <c r="T19" s="16" t="n"/>
+      <c r="U19" s="16" t="n"/>
+      <c r="V19" s="13" t="n"/>
       <c r="W19" s="13" t="n">
         <v>0</v>
       </c>
@@ -5960,10 +4866,7 @@
       <c r="G20" s="14" t="n">
         <v>87087</v>
       </c>
-      <c r="H20" s="15">
-        <f>TEXT(Tabla5[[#This Row], [Fecha]],"MMMM") &amp; TEXT(Tabla5[[#This Row], [Fecha]],"yy")</f>
-        <v/>
-      </c>
+      <c r="H20" s="15" t="n"/>
       <c r="I20" s="16" t="n">
         <v>2</v>
       </c>
@@ -5972,38 +4875,14 @@
       <c r="L20" s="28" t="n"/>
       <c r="M20" s="28" t="n"/>
       <c r="N20" s="16" t="n"/>
-      <c r="O20" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="P20" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="Q20" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="R20" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="S20" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&lt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="T20" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&gt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="U20" s="16">
-        <f>IFERROR(Tabla5[[#This Row], [CANT VENDIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
-      <c r="V20" s="13">
-        <f>IFERROR(Tabla5[[#This Row], [CANT ADQUIRIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
+      <c r="O20" s="16" t="n"/>
+      <c r="P20" s="16" t="n"/>
+      <c r="Q20" s="16" t="n"/>
+      <c r="R20" s="16" t="n"/>
+      <c r="S20" s="16" t="n"/>
+      <c r="T20" s="16" t="n"/>
+      <c r="U20" s="16" t="n"/>
+      <c r="V20" s="13" t="n"/>
       <c r="W20" s="13" t="n">
         <v>39841.2</v>
       </c>
@@ -6020,35 +4899,22 @@
           <t>MB-197467</t>
         </is>
       </c>
-      <c r="C21" s="15" t="inlineStr">
-        <is>
-          <t>#N/A</t>
-        </is>
-      </c>
-      <c r="D21" s="14" t="inlineStr">
-        <is>
-          <t>#N/A</t>
-        </is>
-      </c>
-      <c r="E21" s="15" t="inlineStr">
-        <is>
-          <t>#N/A</t>
-        </is>
-      </c>
-      <c r="F21" s="14" t="inlineStr">
-        <is>
-          <t>#N/A</t>
-        </is>
-      </c>
-      <c r="G21" s="14" t="inlineStr">
-        <is>
-          <t>#N/A</t>
-        </is>
-      </c>
-      <c r="H21" s="15">
-        <f>TEXT(Tabla5[[#This Row], [Fecha]],"MMMM") &amp; TEXT(Tabla5[[#This Row], [Fecha]],"yy")</f>
-        <v/>
-      </c>
+      <c r="C21" s="15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D21" s="14" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E21" s="15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F21" s="14" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G21" s="14" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H21" s="15" t="n"/>
       <c r="I21" s="16" t="n">
         <v>1</v>
       </c>
@@ -6057,47 +4923,19 @@
       <c r="L21" s="28" t="n"/>
       <c r="M21" s="28" t="n"/>
       <c r="N21" s="16" t="n"/>
-      <c r="O21" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="P21" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="Q21" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="R21" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="S21" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&lt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="T21" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&gt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="U21" s="16">
-        <f>IFERROR(Tabla5[[#This Row], [CANT VENDIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
-      <c r="V21" s="13">
-        <f>IFERROR(Tabla5[[#This Row], [CANT ADQUIRIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
-      <c r="W21" s="14" t="inlineStr">
-        <is>
-          <t>#N/A</t>
-        </is>
-      </c>
-      <c r="X21" s="14" t="inlineStr">
-        <is>
-          <t>#N/A</t>
-        </is>
+      <c r="O21" s="16" t="n"/>
+      <c r="P21" s="16" t="n"/>
+      <c r="Q21" s="16" t="n"/>
+      <c r="R21" s="16" t="n"/>
+      <c r="S21" s="16" t="n"/>
+      <c r="T21" s="16" t="n"/>
+      <c r="U21" s="16" t="n"/>
+      <c r="V21" s="13" t="n"/>
+      <c r="W21" s="14" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="X21" s="14" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="22" ht="18.75" customHeight="1">
@@ -6134,10 +4972,7 @@
           <t>ch-37</t>
         </is>
       </c>
-      <c r="H22" s="15">
-        <f>TEXT(Tabla5[[#This Row], [Fecha]],"MMMM") &amp; TEXT(Tabla5[[#This Row], [Fecha]],"yy")</f>
-        <v/>
-      </c>
+      <c r="H22" s="15" t="n"/>
       <c r="I22" s="16" t="n">
         <v>2</v>
       </c>
@@ -6146,38 +4981,14 @@
       <c r="L22" s="28" t="n"/>
       <c r="M22" s="28" t="n"/>
       <c r="N22" s="16" t="n"/>
-      <c r="O22" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="P22" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="Q22" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="R22" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="S22" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&lt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="T22" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&gt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="U22" s="16">
-        <f>IFERROR(Tabla5[[#This Row], [CANT VENDIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
-      <c r="V22" s="13">
-        <f>IFERROR(Tabla5[[#This Row], [CANT ADQUIRIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
+      <c r="O22" s="16" t="n"/>
+      <c r="P22" s="16" t="n"/>
+      <c r="Q22" s="16" t="n"/>
+      <c r="R22" s="16" t="n"/>
+      <c r="S22" s="16" t="n"/>
+      <c r="T22" s="16" t="n"/>
+      <c r="U22" s="16" t="n"/>
+      <c r="V22" s="13" t="n"/>
       <c r="W22" s="13" t="n">
         <v>12958.624</v>
       </c>
@@ -6215,10 +5026,7 @@
           <t>ch-37</t>
         </is>
       </c>
-      <c r="H23" s="15">
-        <f>TEXT(Tabla5[[#This Row], [Fecha]],"MMMM") &amp; TEXT(Tabla5[[#This Row], [Fecha]],"yy")</f>
-        <v/>
-      </c>
+      <c r="H23" s="15" t="n"/>
       <c r="I23" s="16" t="n">
         <v>1</v>
       </c>
@@ -6227,38 +5035,14 @@
       <c r="L23" s="28" t="n"/>
       <c r="M23" s="28" t="n"/>
       <c r="N23" s="16" t="n"/>
-      <c r="O23" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="P23" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="Q23" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="R23" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="S23" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&lt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="T23" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&gt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="U23" s="16">
-        <f>IFERROR(Tabla5[[#This Row], [CANT VENDIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
-      <c r="V23" s="13">
-        <f>IFERROR(Tabla5[[#This Row], [CANT ADQUIRIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
+      <c r="O23" s="16" t="n"/>
+      <c r="P23" s="16" t="n"/>
+      <c r="Q23" s="16" t="n"/>
+      <c r="R23" s="16" t="n"/>
+      <c r="S23" s="16" t="n"/>
+      <c r="T23" s="16" t="n"/>
+      <c r="U23" s="16" t="n"/>
+      <c r="V23" s="13" t="n"/>
       <c r="W23" s="13" t="n">
         <v>0</v>
       </c>
@@ -6300,10 +5084,7 @@
           <t>ch-78</t>
         </is>
       </c>
-      <c r="H24" s="15">
-        <f>TEXT(Tabla5[[#This Row], [Fecha]],"MMMM") &amp; TEXT(Tabla5[[#This Row], [Fecha]],"yy")</f>
-        <v/>
-      </c>
+      <c r="H24" s="15" t="n"/>
       <c r="I24" s="16" t="n">
         <v>1</v>
       </c>
@@ -6312,38 +5093,14 @@
       <c r="L24" s="28" t="n"/>
       <c r="M24" s="28" t="n"/>
       <c r="N24" s="16" t="n"/>
-      <c r="O24" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="P24" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="Q24" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="R24" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="S24" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&lt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="T24" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&gt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="U24" s="16">
-        <f>IFERROR(Tabla5[[#This Row], [CANT VENDIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
-      <c r="V24" s="13">
-        <f>IFERROR(Tabla5[[#This Row], [CANT ADQUIRIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
+      <c r="O24" s="16" t="n"/>
+      <c r="P24" s="16" t="n"/>
+      <c r="Q24" s="16" t="n"/>
+      <c r="R24" s="16" t="n"/>
+      <c r="S24" s="16" t="n"/>
+      <c r="T24" s="16" t="n"/>
+      <c r="U24" s="16" t="n"/>
+      <c r="V24" s="13" t="n"/>
       <c r="W24" s="13" t="n">
         <v>13768.538</v>
       </c>
@@ -6383,10 +5140,7 @@
           <t>ch-38</t>
         </is>
       </c>
-      <c r="H25" s="15">
-        <f>TEXT(Tabla5[[#This Row], [Fecha]],"MMMM") &amp; TEXT(Tabla5[[#This Row], [Fecha]],"yy")</f>
-        <v/>
-      </c>
+      <c r="H25" s="15" t="n"/>
       <c r="I25" s="16" t="n">
         <v>3</v>
       </c>
@@ -6395,38 +5149,14 @@
       <c r="L25" s="28" t="n"/>
       <c r="M25" s="28" t="n"/>
       <c r="N25" s="16" t="n"/>
-      <c r="O25" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="P25" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="Q25" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="R25" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="S25" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&lt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="T25" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&gt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="U25" s="16">
-        <f>IFERROR(Tabla5[[#This Row], [CANT VENDIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
-      <c r="V25" s="13">
-        <f>IFERROR(Tabla5[[#This Row], [CANT ADQUIRIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
+      <c r="O25" s="16" t="n"/>
+      <c r="P25" s="16" t="n"/>
+      <c r="Q25" s="16" t="n"/>
+      <c r="R25" s="16" t="n"/>
+      <c r="S25" s="16" t="n"/>
+      <c r="T25" s="16" t="n"/>
+      <c r="U25" s="16" t="n"/>
+      <c r="V25" s="13" t="n"/>
       <c r="W25" s="13" t="n">
         <v>9800</v>
       </c>
@@ -6468,10 +5198,7 @@
           <t>SK-503F2</t>
         </is>
       </c>
-      <c r="H26" s="15">
-        <f>TEXT(Tabla5[[#This Row], [Fecha]],"MMMM") &amp; TEXT(Tabla5[[#This Row], [Fecha]],"yy")</f>
-        <v/>
-      </c>
+      <c r="H26" s="15" t="n"/>
       <c r="I26" s="16" t="n">
         <v>1</v>
       </c>
@@ -6480,38 +5207,14 @@
       <c r="L26" s="28" t="n"/>
       <c r="M26" s="28" t="n"/>
       <c r="N26" s="16" t="n"/>
-      <c r="O26" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="P26" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="Q26" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="R26" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="S26" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&lt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="T26" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&gt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="U26" s="16">
-        <f>IFERROR(Tabla5[[#This Row], [CANT VENDIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
-      <c r="V26" s="13">
-        <f>IFERROR(Tabla5[[#This Row], [CANT ADQUIRIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
+      <c r="O26" s="16" t="n"/>
+      <c r="P26" s="16" t="n"/>
+      <c r="Q26" s="16" t="n"/>
+      <c r="R26" s="16" t="n"/>
+      <c r="S26" s="16" t="n"/>
+      <c r="T26" s="16" t="n"/>
+      <c r="U26" s="16" t="n"/>
+      <c r="V26" s="13" t="n"/>
       <c r="W26" s="13" t="n">
         <v>0</v>
       </c>
@@ -6551,10 +5254,7 @@
           <t>tenscli</t>
         </is>
       </c>
-      <c r="H27" s="15">
-        <f>TEXT(Tabla5[[#This Row], [Fecha]],"MMMM") &amp; TEXT(Tabla5[[#This Row], [Fecha]],"yy")</f>
-        <v/>
-      </c>
+      <c r="H27" s="15" t="n"/>
       <c r="I27" s="16" t="n">
         <v>2</v>
       </c>
@@ -6563,38 +5263,14 @@
       <c r="L27" s="28" t="n"/>
       <c r="M27" s="28" t="n"/>
       <c r="N27" s="16" t="n"/>
-      <c r="O27" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="P27" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="Q27" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="R27" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="S27" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&lt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="T27" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&gt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="U27" s="16">
-        <f>IFERROR(Tabla5[[#This Row], [CANT VENDIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
-      <c r="V27" s="13">
-        <f>IFERROR(Tabla5[[#This Row], [CANT ADQUIRIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
+      <c r="O27" s="16" t="n"/>
+      <c r="P27" s="16" t="n"/>
+      <c r="Q27" s="16" t="n"/>
+      <c r="R27" s="16" t="n"/>
+      <c r="S27" s="16" t="n"/>
+      <c r="T27" s="16" t="n"/>
+      <c r="U27" s="16" t="n"/>
+      <c r="V27" s="13" t="n"/>
       <c r="W27" s="13" t="n">
         <v>40000</v>
       </c>
@@ -6634,10 +5310,7 @@
           <t>trensym</t>
         </is>
       </c>
-      <c r="H28" s="15">
-        <f>TEXT(Tabla5[[#This Row], [Fecha]],"MMMM") &amp; TEXT(Tabla5[[#This Row], [Fecha]],"yy")</f>
-        <v/>
-      </c>
+      <c r="H28" s="15" t="n"/>
       <c r="I28" s="16" t="n">
         <v>1</v>
       </c>
@@ -6646,38 +5319,14 @@
       <c r="L28" s="28" t="n"/>
       <c r="M28" s="28" t="n"/>
       <c r="N28" s="16" t="n"/>
-      <c r="O28" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="P28" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="Q28" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="R28" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="S28" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&lt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="T28" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&gt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="U28" s="16">
-        <f>IFERROR(Tabla5[[#This Row], [CANT VENDIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
-      <c r="V28" s="13">
-        <f>IFERROR(Tabla5[[#This Row], [CANT ADQUIRIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
+      <c r="O28" s="16" t="n"/>
+      <c r="P28" s="16" t="n"/>
+      <c r="Q28" s="16" t="n"/>
+      <c r="R28" s="16" t="n"/>
+      <c r="S28" s="16" t="n"/>
+      <c r="T28" s="16" t="n"/>
+      <c r="U28" s="16" t="n"/>
+      <c r="V28" s="13" t="n"/>
       <c r="W28" s="13" t="n">
         <v>40000</v>
       </c>
@@ -6717,10 +5366,7 @@
           <t>trabarosca</t>
         </is>
       </c>
-      <c r="H29" s="15">
-        <f>TEXT(Tabla5[[#This Row], [Fecha]],"MMMM") &amp; TEXT(Tabla5[[#This Row], [Fecha]],"yy")</f>
-        <v/>
-      </c>
+      <c r="H29" s="15" t="n"/>
       <c r="I29" s="16" t="n">
         <v>3</v>
       </c>
@@ -6729,38 +5375,14 @@
       <c r="L29" s="28" t="n"/>
       <c r="M29" s="28" t="n"/>
       <c r="N29" s="16" t="n"/>
-      <c r="O29" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="P29" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="Q29" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="R29" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="S29" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&lt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="T29" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&gt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="U29" s="16">
-        <f>IFERROR(Tabla5[[#This Row], [CANT VENDIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
-      <c r="V29" s="13">
-        <f>IFERROR(Tabla5[[#This Row], [CANT ADQUIRIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
+      <c r="O29" s="16" t="n"/>
+      <c r="P29" s="16" t="n"/>
+      <c r="Q29" s="16" t="n"/>
+      <c r="R29" s="16" t="n"/>
+      <c r="S29" s="16" t="n"/>
+      <c r="T29" s="16" t="n"/>
+      <c r="U29" s="16" t="n"/>
+      <c r="V29" s="13" t="n"/>
       <c r="W29" s="13" t="n">
         <v>10000</v>
       </c>
@@ -6802,10 +5424,7 @@
           <t>trabarosca</t>
         </is>
       </c>
-      <c r="H30" s="15">
-        <f>TEXT(Tabla5[[#This Row], [Fecha]],"MMMM") &amp; TEXT(Tabla5[[#This Row], [Fecha]],"yy")</f>
-        <v/>
-      </c>
+      <c r="H30" s="15" t="n"/>
       <c r="I30" s="16" t="n">
         <v>6</v>
       </c>
@@ -6814,38 +5433,14 @@
       <c r="L30" s="28" t="n"/>
       <c r="M30" s="28" t="n"/>
       <c r="N30" s="16" t="n"/>
-      <c r="O30" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="P30" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="Q30" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="R30" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="S30" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&lt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="T30" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&gt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="U30" s="16">
-        <f>IFERROR(Tabla5[[#This Row], [CANT VENDIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
-      <c r="V30" s="13">
-        <f>IFERROR(Tabla5[[#This Row], [CANT ADQUIRIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
+      <c r="O30" s="16" t="n"/>
+      <c r="P30" s="16" t="n"/>
+      <c r="Q30" s="16" t="n"/>
+      <c r="R30" s="16" t="n"/>
+      <c r="S30" s="16" t="n"/>
+      <c r="T30" s="16" t="n"/>
+      <c r="U30" s="16" t="n"/>
+      <c r="V30" s="13" t="n"/>
       <c r="W30" s="13" t="n">
         <v>0</v>
       </c>
@@ -6885,10 +5480,7 @@
           <t>cv07353</t>
         </is>
       </c>
-      <c r="H31" s="15">
-        <f>TEXT(Tabla5[[#This Row], [Fecha]],"MMMM") &amp; TEXT(Tabla5[[#This Row], [Fecha]],"yy")</f>
-        <v/>
-      </c>
+      <c r="H31" s="15" t="n"/>
       <c r="I31" s="16" t="n">
         <v>1</v>
       </c>
@@ -6897,38 +5489,14 @@
       <c r="L31" s="28" t="n"/>
       <c r="M31" s="28" t="n"/>
       <c r="N31" s="16" t="n"/>
-      <c r="O31" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="P31" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="Q31" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="R31" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="S31" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&lt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="T31" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&gt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="U31" s="16">
-        <f>IFERROR(Tabla5[[#This Row], [CANT VENDIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
-      <c r="V31" s="13">
-        <f>IFERROR(Tabla5[[#This Row], [CANT ADQUIRIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
+      <c r="O31" s="16" t="n"/>
+      <c r="P31" s="16" t="n"/>
+      <c r="Q31" s="16" t="n"/>
+      <c r="R31" s="16" t="n"/>
+      <c r="S31" s="16" t="n"/>
+      <c r="T31" s="16" t="n"/>
+      <c r="U31" s="16" t="n"/>
+      <c r="V31" s="13" t="n"/>
       <c r="W31" s="13" t="n">
         <v>0</v>
       </c>
@@ -6968,10 +5536,7 @@
           <t>KCA-7004</t>
         </is>
       </c>
-      <c r="H32" s="15">
-        <f>TEXT(Tabla5[[#This Row], [Fecha]],"MMMM") &amp; TEXT(Tabla5[[#This Row], [Fecha]],"yy")</f>
-        <v/>
-      </c>
+      <c r="H32" s="15" t="n"/>
       <c r="I32" s="16" t="n">
         <v>2</v>
       </c>
@@ -6980,38 +5545,14 @@
       <c r="L32" s="28" t="n"/>
       <c r="M32" s="28" t="n"/>
       <c r="N32" s="16" t="n"/>
-      <c r="O32" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="P32" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="Q32" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="R32" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="S32" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&lt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="T32" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&gt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="U32" s="16">
-        <f>IFERROR(Tabla5[[#This Row], [CANT VENDIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
-      <c r="V32" s="13">
-        <f>IFERROR(Tabla5[[#This Row], [CANT ADQUIRIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
+      <c r="O32" s="16" t="n"/>
+      <c r="P32" s="16" t="n"/>
+      <c r="Q32" s="16" t="n"/>
+      <c r="R32" s="16" t="n"/>
+      <c r="S32" s="16" t="n"/>
+      <c r="T32" s="16" t="n"/>
+      <c r="U32" s="16" t="n"/>
+      <c r="V32" s="13" t="n"/>
       <c r="W32" s="13" t="n">
         <v>52700</v>
       </c>
@@ -7053,10 +5594,7 @@
           <t>KRE-6206</t>
         </is>
       </c>
-      <c r="H33" s="15">
-        <f>TEXT(Tabla5[[#This Row], [Fecha]],"MMMM") &amp; TEXT(Tabla5[[#This Row], [Fecha]],"yy")</f>
-        <v/>
-      </c>
+      <c r="H33" s="15" t="n"/>
       <c r="I33" s="16" t="n">
         <v>1</v>
       </c>
@@ -7065,38 +5603,14 @@
       <c r="L33" s="28" t="n"/>
       <c r="M33" s="28" t="n"/>
       <c r="N33" s="16" t="n"/>
-      <c r="O33" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="P33" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="Q33" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="R33" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="S33" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&lt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="T33" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&gt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="U33" s="16">
-        <f>IFERROR(Tabla5[[#This Row], [CANT VENDIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
-      <c r="V33" s="13">
-        <f>IFERROR(Tabla5[[#This Row], [CANT ADQUIRIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
+      <c r="O33" s="16" t="n"/>
+      <c r="P33" s="16" t="n"/>
+      <c r="Q33" s="16" t="n"/>
+      <c r="R33" s="16" t="n"/>
+      <c r="S33" s="16" t="n"/>
+      <c r="T33" s="16" t="n"/>
+      <c r="U33" s="16" t="n"/>
+      <c r="V33" s="13" t="n"/>
       <c r="W33" s="13" t="n">
         <v>20016.1</v>
       </c>
@@ -7138,10 +5652,7 @@
           <t>KCA-7001</t>
         </is>
       </c>
-      <c r="H34" s="15">
-        <f>TEXT(Tabla5[[#This Row], [Fecha]],"MMMM") &amp; TEXT(Tabla5[[#This Row], [Fecha]],"yy")</f>
-        <v/>
-      </c>
+      <c r="H34" s="15" t="n"/>
       <c r="I34" s="16" t="n">
         <v>1</v>
       </c>
@@ -7150,38 +5661,14 @@
       <c r="L34" s="28" t="n"/>
       <c r="M34" s="28" t="n"/>
       <c r="N34" s="16" t="n"/>
-      <c r="O34" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="P34" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="Q34" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="R34" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="S34" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&lt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="T34" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&gt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="U34" s="16">
-        <f>IFERROR(Tabla5[[#This Row], [CANT VENDIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
-      <c r="V34" s="13">
-        <f>IFERROR(Tabla5[[#This Row], [CANT ADQUIRIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
+      <c r="O34" s="16" t="n"/>
+      <c r="P34" s="16" t="n"/>
+      <c r="Q34" s="16" t="n"/>
+      <c r="R34" s="16" t="n"/>
+      <c r="S34" s="16" t="n"/>
+      <c r="T34" s="16" t="n"/>
+      <c r="U34" s="16" t="n"/>
+      <c r="V34" s="13" t="n"/>
       <c r="W34" s="13" t="n">
         <v>78504.3</v>
       </c>
@@ -7219,10 +5706,7 @@
           <t>tijclime</t>
         </is>
       </c>
-      <c r="H35" s="15">
-        <f>TEXT(Tabla5[[#This Row], [Fecha]],"MMMM") &amp; TEXT(Tabla5[[#This Row], [Fecha]],"yy")</f>
-        <v/>
-      </c>
+      <c r="H35" s="15" t="n"/>
       <c r="I35" s="16" t="n">
         <v>1</v>
       </c>
@@ -7231,38 +5715,14 @@
       <c r="L35" s="28" t="n"/>
       <c r="M35" s="28" t="n"/>
       <c r="N35" s="16" t="n"/>
-      <c r="O35" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="P35" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="Q35" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="R35" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="S35" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&lt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="T35" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&gt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="U35" s="16">
-        <f>IFERROR(Tabla5[[#This Row], [CANT VENDIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
-      <c r="V35" s="13">
-        <f>IFERROR(Tabla5[[#This Row], [CANT ADQUIRIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
+      <c r="O35" s="16" t="n"/>
+      <c r="P35" s="16" t="n"/>
+      <c r="Q35" s="16" t="n"/>
+      <c r="R35" s="16" t="n"/>
+      <c r="S35" s="16" t="n"/>
+      <c r="T35" s="16" t="n"/>
+      <c r="U35" s="16" t="n"/>
+      <c r="V35" s="13" t="n"/>
       <c r="W35" s="13" t="n">
         <v>0</v>
       </c>
@@ -7304,10 +5764,7 @@
           <t>54501-07160</t>
         </is>
       </c>
-      <c r="H36" s="15">
-        <f>TEXT(Tabla5[[#This Row], [Fecha]],"MMMM") &amp; TEXT(Tabla5[[#This Row], [Fecha]],"yy")</f>
-        <v/>
-      </c>
+      <c r="H36" s="15" t="n"/>
       <c r="I36" s="16" t="n">
         <v>1</v>
       </c>
@@ -7316,38 +5773,14 @@
       <c r="L36" s="28" t="n"/>
       <c r="M36" s="28" t="n"/>
       <c r="N36" s="16" t="n"/>
-      <c r="O36" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="P36" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="Q36" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="R36" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="S36" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&lt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="T36" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&gt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="U36" s="16">
-        <f>IFERROR(Tabla5[[#This Row], [CANT VENDIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
-      <c r="V36" s="13">
-        <f>IFERROR(Tabla5[[#This Row], [CANT ADQUIRIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
+      <c r="O36" s="16" t="n"/>
+      <c r="P36" s="16" t="n"/>
+      <c r="Q36" s="16" t="n"/>
+      <c r="R36" s="16" t="n"/>
+      <c r="S36" s="16" t="n"/>
+      <c r="T36" s="16" t="n"/>
+      <c r="U36" s="16" t="n"/>
+      <c r="V36" s="13" t="n"/>
       <c r="W36" s="13" t="n">
         <v>87278.17</v>
       </c>
@@ -7387,10 +5820,7 @@
           <t>45202-77a00</t>
         </is>
       </c>
-      <c r="H37" s="15">
-        <f>TEXT(Tabla5[[#This Row], [Fecha]],"MMMM") &amp; TEXT(Tabla5[[#This Row], [Fecha]],"yy")</f>
-        <v/>
-      </c>
+      <c r="H37" s="15" t="n"/>
       <c r="I37" s="16" t="n">
         <v>2</v>
       </c>
@@ -7399,38 +5829,14 @@
       <c r="L37" s="28" t="n"/>
       <c r="M37" s="28" t="n"/>
       <c r="N37" s="16" t="n"/>
-      <c r="O37" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="P37" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="Q37" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="R37" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="S37" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&lt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="T37" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&gt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="U37" s="16">
-        <f>IFERROR(Tabla5[[#This Row], [CANT VENDIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
-      <c r="V37" s="13">
-        <f>IFERROR(Tabla5[[#This Row], [CANT ADQUIRIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
+      <c r="O37" s="16" t="n"/>
+      <c r="P37" s="16" t="n"/>
+      <c r="Q37" s="16" t="n"/>
+      <c r="R37" s="16" t="n"/>
+      <c r="S37" s="16" t="n"/>
+      <c r="T37" s="16" t="n"/>
+      <c r="U37" s="16" t="n"/>
+      <c r="V37" s="13" t="n"/>
       <c r="W37" s="13" t="n">
         <v>45000</v>
       </c>
@@ -7470,10 +5876,7 @@
           <t>45202-77a00</t>
         </is>
       </c>
-      <c r="H38" s="15">
-        <f>TEXT(Tabla5[[#This Row], [Fecha]],"MMMM") &amp; TEXT(Tabla5[[#This Row], [Fecha]],"yy")</f>
-        <v/>
-      </c>
+      <c r="H38" s="15" t="n"/>
       <c r="I38" s="16" t="n">
         <v>2</v>
       </c>
@@ -7482,38 +5885,14 @@
       <c r="L38" s="28" t="n"/>
       <c r="M38" s="28" t="n"/>
       <c r="N38" s="16" t="n"/>
-      <c r="O38" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="P38" s="16">
-        <f>IF(Tabla5[[#This Row], [¿perdida anormal?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="Q38" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&lt;0")*-1,0)</f>
-        <v/>
-      </c>
-      <c r="R38" s="16">
-        <f>IF(Tabla5[[#This Row], [¿devolución?]]=1,SUMIF(Tabla5[[#This Row], [cantidad]],"&gt;0"),0)</f>
-        <v/>
-      </c>
-      <c r="S38" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&lt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="T38" s="16">
-        <f>SUMIFS(Tabla5[[#This Row], [cantidad]],Tabla5[[#This Row], [cantidad]],"&gt;0",Tabla5[[#This Row], [¿devolución?]],"",Tabla5[[#This Row], [¿perdida anormal?]],"")</f>
-        <v/>
-      </c>
-      <c r="U38" s="16">
-        <f>IFERROR(Tabla5[[#This Row], [CANT VENDIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
-      <c r="V38" s="13">
-        <f>IFERROR(Tabla5[[#This Row], [CANT ADQUIRIDA]]*Tabla5[[#This Row], [Costo unitario]],0)</f>
-        <v/>
-      </c>
+      <c r="O38" s="16" t="n"/>
+      <c r="P38" s="16" t="n"/>
+      <c r="Q38" s="16" t="n"/>
+      <c r="R38" s="16" t="n"/>
+      <c r="S38" s="16" t="n"/>
+      <c r="T38" s="16" t="n"/>
+      <c r="U38" s="16" t="n"/>
+      <c r="V38" s="13" t="n"/>
       <c r="W38" s="13" t="n">
         <v>45000</v>
       </c>

--- a/assets/contabilizacion.xlsx
+++ b/assets/contabilizacion.xlsx
@@ -1130,7 +1130,11 @@
       <c r="B5" s="36" t="n">
         <v>45236</v>
       </c>
-      <c r="C5" s="37" t="n"/>
+      <c r="C5" s="37" t="inlineStr">
+        <is>
+          <t>dasdgd</t>
+        </is>
+      </c>
       <c r="D5" s="37" t="inlineStr">
         <is>
           <t>shdjfh</t>
@@ -1257,7 +1261,9 @@
       <c r="B8" s="36" t="n">
         <v>45236</v>
       </c>
-      <c r="C8" s="37" t="n"/>
+      <c r="C8" s="37" t="n">
+        <v>21333</v>
+      </c>
       <c r="D8" s="37" t="n"/>
       <c r="E8" s="28" t="inlineStr">
         <is>

--- a/assets/contabilizacion.xlsx
+++ b/assets/contabilizacion.xlsx
@@ -993,7 +993,10 @@
           <t>2023-11-06 00:00:00</t>
         </is>
       </c>
-      <c r="C2" s="37" t="n"/>
+      <c r="C2" s="37">
+        <f>2345*45643</f>
+        <v/>
+      </c>
       <c r="D2" s="37" t="inlineStr">
         <is>
           <t>21244</t>
@@ -1038,15 +1041,13 @@
       <c r="B3" s="36" t="n">
         <v>45236</v>
       </c>
-      <c r="C3" s="37" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="D3" s="37" t="inlineStr">
-        <is>
-          <t>fnn</t>
-        </is>
+      <c r="C3" s="37">
+        <f>C2*D2</f>
+        <v/>
+      </c>
+      <c r="D3" s="37">
+        <f>C2+C7</f>
+        <v/>
       </c>
       <c r="E3" s="28" t="inlineStr">
         <is>
@@ -1087,12 +1088,15 @@
       <c r="B4" s="36" t="n">
         <v>45236</v>
       </c>
-      <c r="C4" s="37" t="inlineStr">
-        <is>
-          <t>sdg</t>
-        </is>
-      </c>
-      <c r="D4" s="37" t="n"/>
+      <c r="C4" s="37">
+        <f>23453*336543</f>
+        <v/>
+      </c>
+      <c r="D4" s="37" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="E4" s="28" t="inlineStr">
         <is>
           <t>aveo correa reparitcion 300 nequi 40 efecitvo</t>
@@ -1222,7 +1226,9 @@
       <c r="B7" s="36" t="n">
         <v>45236</v>
       </c>
-      <c r="C7" s="37" t="n"/>
+      <c r="C7" s="37" t="n">
+        <v>75816</v>
+      </c>
       <c r="D7" s="37" t="n"/>
       <c r="E7" s="28" t="inlineStr">
         <is>

--- a/assets/contabilizacion.xlsx
+++ b/assets/contabilizacion.xlsx
@@ -993,9 +993,10 @@
           <t>2023-11-06 00:00:00</t>
         </is>
       </c>
-      <c r="C2" s="37">
-        <f>2345*45643</f>
-        <v/>
+      <c r="C2" s="37" t="inlineStr">
+        <is>
+          <t>veapues</t>
+        </is>
       </c>
       <c r="D2" s="37" t="inlineStr">
         <is>
@@ -1041,12 +1042,13 @@
       <c r="B3" s="36" t="n">
         <v>45236</v>
       </c>
-      <c r="C3" s="37">
-        <f>C2*D2</f>
-        <v/>
+      <c r="C3" s="37" t="inlineStr">
+        <is>
+          <t>5hyd</t>
+        </is>
       </c>
       <c r="D3" s="37">
-        <f>C2+C7</f>
+        <f>2345*34421-2314</f>
         <v/>
       </c>
       <c r="E3" s="28" t="inlineStr">
@@ -1141,7 +1143,7 @@
       </c>
       <c r="D5" s="37" t="inlineStr">
         <is>
-          <t>shdjfh</t>
+          <t>assd</t>
         </is>
       </c>
       <c r="E5" s="28" t="inlineStr">
@@ -1653,9 +1655,14 @@
           <t xml:space="preserve">tubo paso agua corsa^ </t>
         </is>
       </c>
-      <c r="C2" s="28" t="n"/>
-      <c r="D2" s="16" t="n">
-        <v>35000</v>
+      <c r="C2" s="28" t="inlineStr">
+        <is>
+          <t>mirandacon</t>
+        </is>
+      </c>
+      <c r="D2" s="16">
+        <f>2355*2345</f>
+        <v/>
       </c>
       <c r="E2" s="16" t="n">
         <v>9800</v>
@@ -1697,8 +1704,9 @@
           <t>PARTMO</t>
         </is>
       </c>
-      <c r="D3" s="16" t="n">
-        <v>15000</v>
+      <c r="D3" s="16">
+        <f>E2*E4</f>
+        <v/>
       </c>
       <c r="E3" s="16" t="n">
         <v>10600</v>
@@ -3855,13 +3863,14 @@
       <c r="B2" s="18" t="n">
         <v>166</v>
       </c>
-      <c r="C2" s="15" t="inlineStr">
-        <is>
-          <t>323</t>
-        </is>
-      </c>
-      <c r="D2" s="13" t="n">
-        <v>0</v>
+      <c r="C2" s="15">
+        <f>B2*I3</f>
+        <v/>
+      </c>
+      <c r="D2" s="13" t="inlineStr">
+        <is>
+          <t>miraculous</t>
+        </is>
       </c>
       <c r="E2" s="15" t="inlineStr">
         <is>
@@ -3914,10 +3923,9 @@
           <t>varilla medidora de aceite megane clio symbol</t>
         </is>
       </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>CYT</t>
-        </is>
+      <c r="D3" s="14">
+        <f>I3*I4</f>
+        <v/>
       </c>
       <c r="E3" s="15" t="inlineStr">
         <is>

--- a/assets/contabilizacion.xlsx
+++ b/assets/contabilizacion.xlsx
@@ -1012,7 +1012,10 @@
       <c r="G2" s="38" t="n">
         <v>-30000</v>
       </c>
-      <c r="H2" s="16" t="n"/>
+      <c r="H2" s="16">
+        <f>456*3456</f>
+        <v/>
+      </c>
       <c r="I2" s="16" t="n"/>
       <c r="J2" s="39" t="n"/>
       <c r="K2" s="40" t="n"/>

--- a/assets/contabilizacion.xlsx
+++ b/assets/contabilizacion.xlsx
@@ -1111,7 +1111,11 @@
         <v>40000</v>
       </c>
       <c r="G4" s="38" t="n"/>
-      <c r="H4" s="16" t="n"/>
+      <c r="H4" s="16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="I4" s="16" t="n"/>
       <c r="J4" s="39" t="n"/>
       <c r="K4" s="40" t="n"/>
@@ -1158,7 +1162,10 @@
         <v>100000</v>
       </c>
       <c r="G5" s="38" t="n"/>
-      <c r="H5" s="16" t="n"/>
+      <c r="H5" s="16">
+        <f>2356*4432</f>
+        <v/>
+      </c>
       <c r="I5" s="16" t="n"/>
       <c r="J5" s="39" t="n"/>
       <c r="K5" s="40" t="n"/>
@@ -1203,7 +1210,10 @@
       <c r="G6" s="38" t="n">
         <v>-15000</v>
       </c>
-      <c r="H6" s="16" t="n"/>
+      <c r="H6" s="16">
+        <f>G6+3443021</f>
+        <v/>
+      </c>
       <c r="I6" s="16" t="n"/>
       <c r="J6" s="39" t="n"/>
       <c r="K6" s="40" t="n"/>

--- a/assets/contabilizacion.xlsx
+++ b/assets/contabilizacion.xlsx
@@ -1254,7 +1254,11 @@
       <c r="G7" s="38" t="n">
         <v>-38000</v>
       </c>
-      <c r="H7" s="16" t="n"/>
+      <c r="H7" s="16" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
       <c r="I7" s="16" t="n"/>
       <c r="J7" s="39" t="n"/>
       <c r="K7" s="40" t="n"/>
@@ -1775,7 +1779,10 @@
           <t>8D-7</t>
         </is>
       </c>
-      <c r="H4" s="28" t="n"/>
+      <c r="H4" s="28">
+        <f>E2*L4+D6-A4*6</f>
+        <v/>
+      </c>
       <c r="I4" s="29" t="n"/>
       <c r="J4" s="28" t="n"/>
       <c r="K4" s="16" t="n"/>

--- a/assets/contabilizacion.xlsx
+++ b/assets/contabilizacion.xlsx
@@ -1200,7 +1200,10 @@
           <t>wueye</t>
         </is>
       </c>
-      <c r="D6" s="37" t="n"/>
+      <c r="D6" s="37">
+        <f>C4*45</f>
+        <v/>
+      </c>
       <c r="E6" s="28" t="inlineStr">
         <is>
           <t>adelanto edison</t>

--- a/assets/contabilizacion.xlsx
+++ b/assets/contabilizacion.xlsx
@@ -1094,7 +1094,7 @@
         <v>45236</v>
       </c>
       <c r="C4" s="37">
-        <f>23453*336543</f>
+        <f>23453*336543+24</f>
         <v/>
       </c>
       <c r="D4" s="37" t="inlineStr">

--- a/assets/contabilizacion.xlsx
+++ b/assets/contabilizacion.xlsx
@@ -1089,7 +1089,11 @@
       <c r="AC3" s="38" t="n"/>
     </row>
     <row r="4" ht="19.5" customHeight="1">
-      <c r="A4" s="36" t="n"/>
+      <c r="A4" s="36" t="inlineStr">
+        <is>
+          <t>15-June-2001</t>
+        </is>
+      </c>
       <c r="B4" s="36" t="n">
         <v>45236</v>
       </c>

--- a/assets/contabilizacion.xlsx
+++ b/assets/contabilizacion.xlsx
@@ -639,6 +639,10 @@
       <c r="E4" s="5" t="n">
         <v>300000</v>
       </c>
+      <c r="F4">
+        <f>23*432</f>
+        <v/>
+      </c>
       <c r="G4" s="5">
         <f>SUM(E4:F4)</f>
         <v/>
@@ -685,6 +689,10 @@
         <is>
           <t>gastos representacion</t>
         </is>
+      </c>
+      <c r="E6">
+        <f>E5+E2</f>
+        <v/>
       </c>
       <c r="F6" s="5" t="n">
         <v>-1000</v>

--- a/assets/contabilizacion.xlsx
+++ b/assets/contabilizacion.xlsx
@@ -672,6 +672,10 @@
         <f>SUM(E5:F5)</f>
         <v/>
       </c>
+      <c r="I5">
+        <f>80SUM/8E4:F49</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">

--- a/assets/contabilizacion.xlsx
+++ b/assets/contabilizacion.xlsx
@@ -673,7 +673,7 @@
         <v/>
       </c>
       <c r="I5">
-        <f>80SUM/8E4:F49</f>
+        <f>SUM(E2:F9)</f>
         <v/>
       </c>
     </row>

--- a/assets/contabilizacion.xlsx
+++ b/assets/contabilizacion.xlsx
@@ -1381,6 +1381,10 @@
           <t>9c-8</t>
         </is>
       </c>
+      <c r="H6">
+        <f>SUM(D2:E12)</f>
+        <v/>
+      </c>
       <c r="I6">
         <f>SUMIFS('entradas y salidas'!I:I,'entradas y salidas'!B:B,productos!A6)</f>
         <v/>

--- a/assets/contabilizacion.xlsx
+++ b/assets/contabilizacion.xlsx
@@ -705,6 +705,11 @@
         <f>SUM(E6:F6)</f>
         <v/>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0SUM8E2:F209</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -728,6 +733,10 @@
       </c>
       <c r="G7" s="5">
         <f>SUM(E7:F7)</f>
+        <v/>
+      </c>
+      <c r="I7">
+        <f>SUM(E2:F9)</f>
         <v/>
       </c>
     </row>

--- a/assets/contabilizacion.xlsx
+++ b/assets/contabilizacion.xlsx
@@ -705,10 +705,9 @@
         <f>SUM(E6:F6)</f>
         <v/>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0SUM8E2:F209</t>
-        </is>
+      <c r="I6">
+        <f>TEXT(A2;"dddd")</f>
+        <v/>
       </c>
     </row>
     <row r="7">
